--- a/output/version3/test/10-5/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>487</v>
+      </c>
+      <c r="C2" t="n">
+        <v>423</v>
+      </c>
+      <c r="D2" t="n">
         <v>455</v>
       </c>
-      <c r="C2" t="n">
-        <v>495</v>
-      </c>
-      <c r="D2" t="n">
-        <v>610</v>
-      </c>
       <c r="E2" t="n">
-        <v>521</v>
+        <v>439</v>
       </c>
       <c r="F2" t="n">
-        <v>511</v>
+        <v>454</v>
       </c>
       <c r="G2" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H2" t="n">
-        <v>479</v>
+        <v>444</v>
       </c>
       <c r="I2" t="n">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="J2" t="n">
-        <v>506</v>
+        <v>430</v>
       </c>
       <c r="K2" t="n">
-        <v>509</v>
+        <v>443</v>
       </c>
       <c r="L2" t="n">
-        <v>512.1</v>
+        <v>458.8</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>534</v>
+        <v>495</v>
       </c>
       <c r="C3" t="n">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="D3" t="n">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="E3" t="n">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="F3" t="n">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="G3" t="n">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="H3" t="n">
-        <v>529</v>
+        <v>504</v>
       </c>
       <c r="I3" t="n">
-        <v>545</v>
+        <v>463</v>
       </c>
       <c r="J3" t="n">
-        <v>617</v>
+        <v>528</v>
       </c>
       <c r="K3" t="n">
-        <v>478</v>
+        <v>542</v>
       </c>
       <c r="L3" t="n">
-        <v>528.5</v>
+        <v>510.7</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>531</v>
+        <v>603</v>
       </c>
       <c r="C4" t="n">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="D4" t="n">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="E4" t="n">
-        <v>553</v>
+        <v>494</v>
       </c>
       <c r="F4" t="n">
-        <v>612</v>
+        <v>517</v>
       </c>
       <c r="G4" t="n">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="H4" t="n">
-        <v>503</v>
+        <v>598</v>
       </c>
       <c r="I4" t="n">
-        <v>577</v>
+        <v>524</v>
       </c>
       <c r="J4" t="n">
-        <v>543</v>
+        <v>462</v>
       </c>
       <c r="K4" t="n">
-        <v>574</v>
+        <v>616</v>
       </c>
       <c r="L4" t="n">
-        <v>554.3</v>
+        <v>546.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>547</v>
+        <v>469</v>
       </c>
       <c r="C5" t="n">
-        <v>486</v>
+        <v>450</v>
       </c>
       <c r="D5" t="n">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="E5" t="n">
-        <v>544</v>
+        <v>500</v>
       </c>
       <c r="F5" t="n">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="G5" t="n">
-        <v>531</v>
+        <v>494</v>
       </c>
       <c r="H5" t="n">
-        <v>517</v>
+        <v>470</v>
       </c>
       <c r="I5" t="n">
-        <v>505</v>
+        <v>466</v>
       </c>
       <c r="J5" t="n">
-        <v>500</v>
+        <v>534</v>
       </c>
       <c r="K5" t="n">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="L5" t="n">
-        <v>505.7</v>
+        <v>479.3</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="C6" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D6" t="n">
-        <v>454</v>
+        <v>536</v>
       </c>
       <c r="E6" t="n">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="F6" t="n">
-        <v>499</v>
+        <v>426</v>
       </c>
       <c r="G6" t="n">
-        <v>523</v>
+        <v>432</v>
       </c>
       <c r="H6" t="n">
-        <v>544</v>
+        <v>509</v>
       </c>
       <c r="I6" t="n">
-        <v>503</v>
+        <v>551</v>
       </c>
       <c r="J6" t="n">
-        <v>547</v>
+        <v>591</v>
       </c>
       <c r="K6" t="n">
-        <v>427</v>
+        <v>512</v>
       </c>
       <c r="L6" t="n">
-        <v>499</v>
+        <v>502.3</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>531</v>
+        <v>474</v>
       </c>
       <c r="C7" t="n">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="E7" t="n">
-        <v>496</v>
+        <v>431</v>
       </c>
       <c r="F7" t="n">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G7" t="n">
-        <v>522</v>
+        <v>401</v>
       </c>
       <c r="H7" t="n">
-        <v>529</v>
+        <v>467</v>
       </c>
       <c r="I7" t="n">
-        <v>467</v>
+        <v>425</v>
       </c>
       <c r="J7" t="n">
-        <v>523</v>
+        <v>471</v>
       </c>
       <c r="K7" t="n">
-        <v>473</v>
+        <v>429</v>
       </c>
       <c r="L7" t="n">
-        <v>495.8</v>
+        <v>447.9</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>579</v>
+        <v>516</v>
       </c>
       <c r="C8" t="n">
-        <v>536</v>
+        <v>445</v>
       </c>
       <c r="D8" t="n">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="E8" t="n">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="F8" t="n">
-        <v>485</v>
+        <v>516</v>
       </c>
       <c r="G8" t="n">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H8" t="n">
-        <v>533</v>
+        <v>457</v>
       </c>
       <c r="I8" t="n">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="J8" t="n">
-        <v>627</v>
+        <v>540</v>
       </c>
       <c r="K8" t="n">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="L8" t="n">
-        <v>531.6</v>
+        <v>505.1</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>505</v>
+        <v>461</v>
       </c>
       <c r="C9" t="n">
-        <v>593</v>
+        <v>424</v>
       </c>
       <c r="D9" t="n">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="E9" t="n">
-        <v>499</v>
+        <v>442</v>
       </c>
       <c r="F9" t="n">
-        <v>535</v>
+        <v>481</v>
       </c>
       <c r="G9" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H9" t="n">
-        <v>571</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="J9" t="n">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="K9" t="n">
-        <v>563</v>
+        <v>487</v>
       </c>
       <c r="L9" t="n">
-        <v>512.7</v>
+        <v>457.6</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>529</v>
+        <v>486</v>
       </c>
       <c r="C10" t="n">
-        <v>513</v>
+        <v>470</v>
       </c>
       <c r="D10" t="n">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="E10" t="n">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F10" t="n">
-        <v>603</v>
+        <v>500</v>
       </c>
       <c r="G10" t="n">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="H10" t="n">
-        <v>543</v>
+        <v>512</v>
       </c>
       <c r="I10" t="n">
-        <v>541</v>
+        <v>580</v>
       </c>
       <c r="J10" t="n">
-        <v>531</v>
+        <v>469</v>
       </c>
       <c r="K10" t="n">
-        <v>541</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>530.7</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>474</v>
+        <v>416</v>
       </c>
       <c r="C11" t="n">
-        <v>497</v>
+        <v>377</v>
       </c>
       <c r="D11" t="n">
-        <v>495</v>
+        <v>377</v>
       </c>
       <c r="E11" t="n">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="F11" t="n">
-        <v>538</v>
+        <v>402</v>
       </c>
       <c r="G11" t="n">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="H11" t="n">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="I11" t="n">
-        <v>449</v>
+        <v>477</v>
       </c>
       <c r="J11" t="n">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="K11" t="n">
-        <v>460</v>
+        <v>419</v>
       </c>
       <c r="L11" t="n">
-        <v>465.8</v>
+        <v>422.4</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="C12" t="n">
-        <v>530</v>
+        <v>476</v>
       </c>
       <c r="D12" t="n">
-        <v>457</v>
+        <v>536</v>
       </c>
       <c r="E12" t="n">
-        <v>611</v>
+        <v>529</v>
       </c>
       <c r="F12" t="n">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="G12" t="n">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="H12" t="n">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="I12" t="n">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="J12" t="n">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="K12" t="n">
-        <v>521</v>
+        <v>575</v>
       </c>
       <c r="L12" t="n">
-        <v>534.6</v>
+        <v>526.8</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>554</v>
+        <v>431</v>
       </c>
       <c r="C13" t="n">
-        <v>520</v>
+        <v>600</v>
       </c>
       <c r="D13" t="n">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="E13" t="n">
-        <v>472</v>
+        <v>559</v>
       </c>
       <c r="F13" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="G13" t="n">
-        <v>418</v>
+        <v>524</v>
       </c>
       <c r="H13" t="n">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="I13" t="n">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="J13" t="n">
-        <v>467</v>
+        <v>588</v>
       </c>
       <c r="K13" t="n">
-        <v>466</v>
+        <v>529</v>
       </c>
       <c r="L13" t="n">
-        <v>491.4</v>
+        <v>523.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>569</v>
+        <v>506</v>
       </c>
       <c r="C14" t="n">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="D14" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E14" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F14" t="n">
-        <v>560</v>
+        <v>526</v>
       </c>
       <c r="G14" t="n">
-        <v>531</v>
+        <v>605</v>
       </c>
       <c r="H14" t="n">
-        <v>583</v>
+        <v>493</v>
       </c>
       <c r="I14" t="n">
-        <v>482</v>
+        <v>577</v>
       </c>
       <c r="J14" t="n">
-        <v>574</v>
+        <v>475</v>
       </c>
       <c r="K14" t="n">
-        <v>552</v>
+        <v>507</v>
       </c>
       <c r="L14" t="n">
-        <v>549</v>
+        <v>530.6</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="C15" t="n">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="D15" t="n">
-        <v>562</v>
+        <v>459</v>
       </c>
       <c r="E15" t="n">
-        <v>665</v>
+        <v>475</v>
       </c>
       <c r="F15" t="n">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="G15" t="n">
-        <v>568</v>
+        <v>519</v>
       </c>
       <c r="H15" t="n">
-        <v>526</v>
+        <v>459</v>
       </c>
       <c r="I15" t="n">
-        <v>492</v>
+        <v>531</v>
       </c>
       <c r="J15" t="n">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="K15" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="L15" t="n">
-        <v>544.1</v>
+        <v>499.9</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>535</v>
+        <v>452</v>
       </c>
       <c r="C16" t="n">
-        <v>523</v>
+        <v>470</v>
       </c>
       <c r="D16" t="n">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E16" t="n">
-        <v>569</v>
+        <v>484</v>
       </c>
       <c r="F16" t="n">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G16" t="n">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="H16" t="n">
+        <v>524</v>
+      </c>
+      <c r="I16" t="n">
         <v>505</v>
       </c>
-      <c r="I16" t="n">
-        <v>544</v>
-      </c>
       <c r="J16" t="n">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="K16" t="n">
-        <v>554</v>
+        <v>448</v>
       </c>
       <c r="L16" t="n">
-        <v>526.3</v>
+        <v>486.3</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="C17" t="n">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D17" t="n">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="E17" t="n">
-        <v>497</v>
+        <v>468</v>
       </c>
       <c r="F17" t="n">
-        <v>458</v>
+        <v>494</v>
       </c>
       <c r="G17" t="n">
-        <v>477</v>
+        <v>417</v>
       </c>
       <c r="H17" t="n">
-        <v>545</v>
+        <v>462</v>
       </c>
       <c r="I17" t="n">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="J17" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="K17" t="n">
-        <v>472</v>
+        <v>560</v>
       </c>
       <c r="L17" t="n">
-        <v>482.6</v>
+        <v>477.6</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
+        <v>540</v>
+      </c>
+      <c r="C18" t="n">
+        <v>588</v>
+      </c>
+      <c r="D18" t="n">
+        <v>584</v>
+      </c>
+      <c r="E18" t="n">
+        <v>602</v>
+      </c>
+      <c r="F18" t="n">
+        <v>540</v>
+      </c>
+      <c r="G18" t="n">
+        <v>550</v>
+      </c>
+      <c r="H18" t="n">
+        <v>556</v>
+      </c>
+      <c r="I18" t="n">
+        <v>478</v>
+      </c>
+      <c r="J18" t="n">
         <v>605</v>
       </c>
-      <c r="C18" t="n">
-        <v>685</v>
-      </c>
-      <c r="D18" t="n">
-        <v>566</v>
-      </c>
-      <c r="E18" t="n">
-        <v>561</v>
-      </c>
-      <c r="F18" t="n">
-        <v>583</v>
-      </c>
-      <c r="G18" t="n">
-        <v>507</v>
-      </c>
-      <c r="H18" t="n">
-        <v>557</v>
-      </c>
-      <c r="I18" t="n">
-        <v>625</v>
-      </c>
-      <c r="J18" t="n">
-        <v>600</v>
-      </c>
       <c r="K18" t="n">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="L18" t="n">
-        <v>585.7</v>
+        <v>562.1</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>566</v>
+        <v>466</v>
       </c>
       <c r="C19" t="n">
-        <v>666</v>
+        <v>564</v>
       </c>
       <c r="D19" t="n">
-        <v>583</v>
+        <v>504</v>
       </c>
       <c r="E19" t="n">
-        <v>563</v>
+        <v>482</v>
       </c>
       <c r="F19" t="n">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="G19" t="n">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="H19" t="n">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="I19" t="n">
-        <v>575</v>
+        <v>509</v>
       </c>
       <c r="J19" t="n">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="K19" t="n">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="L19" t="n">
-        <v>558.7</v>
+        <v>516.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="C20" t="n">
+        <v>594</v>
+      </c>
+      <c r="D20" t="n">
+        <v>548</v>
+      </c>
+      <c r="E20" t="n">
+        <v>602</v>
+      </c>
+      <c r="F20" t="n">
+        <v>565</v>
+      </c>
+      <c r="G20" t="n">
+        <v>492</v>
+      </c>
+      <c r="H20" t="n">
+        <v>642</v>
+      </c>
+      <c r="I20" t="n">
         <v>511</v>
       </c>
-      <c r="D20" t="n">
-        <v>523</v>
-      </c>
-      <c r="E20" t="n">
-        <v>436</v>
-      </c>
-      <c r="F20" t="n">
-        <v>499</v>
-      </c>
-      <c r="G20" t="n">
-        <v>530</v>
-      </c>
-      <c r="H20" t="n">
-        <v>509</v>
-      </c>
-      <c r="I20" t="n">
-        <v>525</v>
-      </c>
       <c r="J20" t="n">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="K20" t="n">
-        <v>475</v>
+        <v>563</v>
       </c>
       <c r="L20" t="n">
-        <v>505.7</v>
+        <v>560.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>462</v>
+        <v>516</v>
       </c>
       <c r="C21" t="n">
-        <v>521</v>
+        <v>486</v>
       </c>
       <c r="D21" t="n">
-        <v>513</v>
+        <v>465</v>
       </c>
       <c r="E21" t="n">
-        <v>596</v>
+        <v>476</v>
       </c>
       <c r="F21" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G21" t="n">
-        <v>555</v>
+        <v>589</v>
       </c>
       <c r="H21" t="n">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="I21" t="n">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="J21" t="n">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="K21" t="n">
-        <v>420</v>
+        <v>528</v>
       </c>
       <c r="L21" t="n">
-        <v>495.5</v>
+        <v>497.2</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>579</v>
+        <v>466</v>
       </c>
       <c r="C22" t="n">
-        <v>668</v>
+        <v>453</v>
       </c>
       <c r="D22" t="n">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="E22" t="n">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="F22" t="n">
-        <v>612</v>
+        <v>450</v>
       </c>
       <c r="G22" t="n">
-        <v>539</v>
+        <v>441</v>
       </c>
       <c r="H22" t="n">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="I22" t="n">
-        <v>582</v>
+        <v>522</v>
       </c>
       <c r="J22" t="n">
-        <v>650</v>
+        <v>546</v>
       </c>
       <c r="K22" t="n">
-        <v>531</v>
+        <v>461</v>
       </c>
       <c r="L22" t="n">
-        <v>574</v>
+        <v>489.6</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>403</v>
+        <v>472</v>
       </c>
       <c r="C23" t="n">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="D23" t="n">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="E23" t="n">
-        <v>442</v>
+        <v>410</v>
       </c>
       <c r="F23" t="n">
-        <v>393</v>
+        <v>450</v>
       </c>
       <c r="G23" t="n">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="H23" t="n">
-        <v>396</v>
+        <v>462</v>
       </c>
       <c r="I23" t="n">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="J23" t="n">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="K23" t="n">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="L23" t="n">
-        <v>427.6</v>
+        <v>440.4</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>424</v>
+        <v>455</v>
       </c>
       <c r="C24" t="n">
-        <v>502</v>
+        <v>465</v>
       </c>
       <c r="D24" t="n">
-        <v>439</v>
+        <v>483</v>
       </c>
       <c r="E24" t="n">
+        <v>520</v>
+      </c>
+      <c r="F24" t="n">
         <v>473</v>
       </c>
-      <c r="F24" t="n">
-        <v>415</v>
-      </c>
       <c r="G24" t="n">
-        <v>415</v>
+        <v>476</v>
       </c>
       <c r="H24" t="n">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="I24" t="n">
-        <v>514</v>
+        <v>436</v>
       </c>
       <c r="J24" t="n">
-        <v>503</v>
+        <v>468</v>
       </c>
       <c r="K24" t="n">
-        <v>429</v>
+        <v>483</v>
       </c>
       <c r="L24" t="n">
-        <v>463.1</v>
+        <v>476.5</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C25" t="n">
-        <v>451</v>
+        <v>390</v>
       </c>
       <c r="D25" t="n">
-        <v>453</v>
+        <v>399</v>
       </c>
       <c r="E25" t="n">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="F25" t="n">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="G25" t="n">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="H25" t="n">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="I25" t="n">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="J25" t="n">
-        <v>468</v>
+        <v>400</v>
       </c>
       <c r="K25" t="n">
-        <v>363</v>
+        <v>515</v>
       </c>
       <c r="L25" t="n">
-        <v>424.7</v>
+        <v>423.5</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>536</v>
+        <v>502</v>
       </c>
       <c r="C26" t="n">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="D26" t="n">
-        <v>596</v>
+        <v>503</v>
       </c>
       <c r="E26" t="n">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="F26" t="n">
-        <v>545</v>
+        <v>637</v>
       </c>
       <c r="G26" t="n">
-        <v>552</v>
+        <v>467</v>
       </c>
       <c r="H26" t="n">
-        <v>564</v>
+        <v>633</v>
       </c>
       <c r="I26" t="n">
-        <v>497</v>
+        <v>607</v>
       </c>
       <c r="J26" t="n">
-        <v>551</v>
+        <v>638</v>
       </c>
       <c r="K26" t="n">
-        <v>581</v>
+        <v>647</v>
       </c>
       <c r="L26" t="n">
-        <v>552.1</v>
+        <v>577.6</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>462</v>
+        <v>416</v>
       </c>
       <c r="C27" t="n">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="D27" t="n">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="E27" t="n">
-        <v>469</v>
+        <v>512</v>
       </c>
       <c r="F27" t="n">
-        <v>434</v>
+        <v>474</v>
       </c>
       <c r="G27" t="n">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H27" t="n">
-        <v>502</v>
+        <v>413</v>
       </c>
       <c r="I27" t="n">
-        <v>501</v>
+        <v>442</v>
       </c>
       <c r="J27" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="K27" t="n">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="L27" t="n">
-        <v>472.2</v>
+        <v>454.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>446</v>
+        <v>516</v>
       </c>
       <c r="C28" t="n">
-        <v>530</v>
+        <v>436</v>
       </c>
       <c r="D28" t="n">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="E28" t="n">
-        <v>536</v>
+        <v>467</v>
       </c>
       <c r="F28" t="n">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="G28" t="n">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="H28" t="n">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="I28" t="n">
-        <v>513</v>
+        <v>452</v>
       </c>
       <c r="J28" t="n">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="K28" t="n">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="L28" t="n">
-        <v>490.9</v>
+        <v>473.9</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C29" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D29" t="n">
-        <v>496</v>
+        <v>459</v>
       </c>
       <c r="E29" t="n">
-        <v>499</v>
+        <v>467</v>
       </c>
       <c r="F29" t="n">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="G29" t="n">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="H29" t="n">
-        <v>490</v>
+        <v>462</v>
       </c>
       <c r="I29" t="n">
-        <v>497</v>
+        <v>535</v>
       </c>
       <c r="J29" t="n">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="K29" t="n">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="L29" t="n">
-        <v>474.8</v>
+        <v>469.2</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>453</v>
+        <v>404</v>
       </c>
       <c r="C30" t="n">
-        <v>598</v>
+        <v>455</v>
       </c>
       <c r="D30" t="n">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>504</v>
+        <v>454</v>
       </c>
       <c r="F30" t="n">
-        <v>428</v>
+        <v>506</v>
       </c>
       <c r="G30" t="n">
-        <v>514</v>
+        <v>451</v>
       </c>
       <c r="H30" t="n">
-        <v>537</v>
+        <v>402</v>
       </c>
       <c r="I30" t="n">
-        <v>451</v>
+        <v>505</v>
       </c>
       <c r="J30" t="n">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="K30" t="n">
-        <v>559</v>
+        <v>455</v>
       </c>
       <c r="L30" t="n">
-        <v>500.5</v>
+        <v>461.1</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="C31" t="n">
-        <v>476</v>
+        <v>521</v>
       </c>
       <c r="D31" t="n">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="E31" t="n">
-        <v>456</v>
+        <v>525</v>
       </c>
       <c r="F31" t="n">
-        <v>509</v>
+        <v>449</v>
       </c>
       <c r="G31" t="n">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="H31" t="n">
-        <v>474</v>
+        <v>525</v>
       </c>
       <c r="I31" t="n">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="J31" t="n">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="K31" t="n">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="L31" t="n">
-        <v>478.3</v>
+        <v>493.5</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>541</v>
+        <v>397</v>
       </c>
       <c r="C32" t="n">
-        <v>464</v>
+        <v>418</v>
       </c>
       <c r="D32" t="n">
-        <v>529</v>
+        <v>480</v>
       </c>
       <c r="E32" t="n">
-        <v>611</v>
+        <v>417</v>
       </c>
       <c r="F32" t="n">
-        <v>500</v>
+        <v>425</v>
       </c>
       <c r="G32" t="n">
-        <v>486</v>
+        <v>439</v>
       </c>
       <c r="H32" t="n">
-        <v>549</v>
+        <v>454</v>
       </c>
       <c r="I32" t="n">
-        <v>503</v>
+        <v>421</v>
       </c>
       <c r="J32" t="n">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="K32" t="n">
-        <v>461</v>
+        <v>419</v>
       </c>
       <c r="L32" t="n">
-        <v>512.8</v>
+        <v>436.5</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>475</v>
+        <v>413</v>
       </c>
       <c r="C33" t="n">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D33" t="n">
-        <v>490</v>
+        <v>401</v>
       </c>
       <c r="E33" t="n">
-        <v>531</v>
+        <v>441</v>
       </c>
       <c r="F33" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G33" t="n">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="H33" t="n">
-        <v>479</v>
+        <v>537</v>
       </c>
       <c r="I33" t="n">
-        <v>486</v>
+        <v>396</v>
       </c>
       <c r="J33" t="n">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="K33" t="n">
-        <v>512</v>
+        <v>416</v>
       </c>
       <c r="L33" t="n">
-        <v>486.3</v>
+        <v>434.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>512</v>
+        <v>411</v>
       </c>
       <c r="C34" t="n">
-        <v>521</v>
+        <v>463</v>
       </c>
       <c r="D34" t="n">
-        <v>447</v>
+        <v>519</v>
       </c>
       <c r="E34" t="n">
-        <v>438</v>
+        <v>472</v>
       </c>
       <c r="F34" t="n">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="G34" t="n">
-        <v>495</v>
+        <v>387</v>
       </c>
       <c r="H34" t="n">
-        <v>532</v>
+        <v>424</v>
       </c>
       <c r="I34" t="n">
-        <v>480</v>
+        <v>449</v>
       </c>
       <c r="J34" t="n">
-        <v>484</v>
+        <v>417</v>
       </c>
       <c r="K34" t="n">
-        <v>402</v>
+        <v>449</v>
       </c>
       <c r="L34" t="n">
-        <v>470.7</v>
+        <v>441.9</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>559</v>
+        <v>498</v>
       </c>
       <c r="C35" t="n">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="D35" t="n">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="E35" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="F35" t="n">
-        <v>526</v>
+        <v>475</v>
       </c>
       <c r="G35" t="n">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="H35" t="n">
-        <v>600</v>
+        <v>557</v>
       </c>
       <c r="I35" t="n">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="J35" t="n">
-        <v>564</v>
+        <v>518</v>
       </c>
       <c r="K35" t="n">
-        <v>552</v>
+        <v>479</v>
       </c>
       <c r="L35" t="n">
-        <v>536</v>
+        <v>514.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C36" t="n">
-        <v>447</v>
+        <v>371</v>
       </c>
       <c r="D36" t="n">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="E36" t="n">
-        <v>533</v>
+        <v>492</v>
       </c>
       <c r="F36" t="n">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="G36" t="n">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="H36" t="n">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="I36" t="n">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="J36" t="n">
-        <v>447</v>
+        <v>386</v>
       </c>
       <c r="K36" t="n">
-        <v>436</v>
+        <v>366</v>
       </c>
       <c r="L36" t="n">
-        <v>435.3</v>
+        <v>402.4</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>491</v>
+        <v>431</v>
       </c>
       <c r="C37" t="n">
-        <v>461</v>
+        <v>497</v>
       </c>
       <c r="D37" t="n">
-        <v>487</v>
+        <v>423</v>
       </c>
       <c r="E37" t="n">
-        <v>472</v>
+        <v>439</v>
       </c>
       <c r="F37" t="n">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="G37" t="n">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="H37" t="n">
-        <v>554</v>
+        <v>460</v>
       </c>
       <c r="I37" t="n">
-        <v>511</v>
+        <v>445</v>
       </c>
       <c r="J37" t="n">
-        <v>508</v>
+        <v>466</v>
       </c>
       <c r="K37" t="n">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="L37" t="n">
-        <v>491.6</v>
+        <v>459.1</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
+        <v>627</v>
+      </c>
+      <c r="C38" t="n">
+        <v>629</v>
+      </c>
+      <c r="D38" t="n">
+        <v>595</v>
+      </c>
+      <c r="E38" t="n">
+        <v>628</v>
+      </c>
+      <c r="F38" t="n">
+        <v>583</v>
+      </c>
+      <c r="G38" t="n">
+        <v>516</v>
+      </c>
+      <c r="H38" t="n">
         <v>579</v>
       </c>
-      <c r="C38" t="n">
-        <v>631</v>
-      </c>
-      <c r="D38" t="n">
-        <v>671</v>
-      </c>
-      <c r="E38" t="n">
-        <v>663</v>
-      </c>
-      <c r="F38" t="n">
-        <v>567</v>
-      </c>
-      <c r="G38" t="n">
-        <v>598</v>
-      </c>
-      <c r="H38" t="n">
-        <v>651</v>
-      </c>
       <c r="I38" t="n">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="J38" t="n">
-        <v>673</v>
+        <v>525</v>
       </c>
       <c r="K38" t="n">
-        <v>693</v>
+        <v>568</v>
       </c>
       <c r="L38" t="n">
-        <v>630.1</v>
+        <v>580.6</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C39" t="n">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="D39" t="n">
-        <v>582</v>
+        <v>436</v>
       </c>
       <c r="E39" t="n">
-        <v>532</v>
+        <v>487</v>
       </c>
       <c r="F39" t="n">
-        <v>468</v>
+        <v>386</v>
       </c>
       <c r="G39" t="n">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="H39" t="n">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="I39" t="n">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="J39" t="n">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="K39" t="n">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="L39" t="n">
-        <v>466.9</v>
+        <v>430.6</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>518</v>
+        <v>464</v>
       </c>
       <c r="C40" t="n">
-        <v>529</v>
+        <v>448</v>
       </c>
       <c r="D40" t="n">
-        <v>498</v>
+        <v>470</v>
       </c>
       <c r="E40" t="n">
-        <v>548</v>
+        <v>473</v>
       </c>
       <c r="F40" t="n">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="G40" t="n">
-        <v>522</v>
+        <v>448</v>
       </c>
       <c r="H40" t="n">
-        <v>529</v>
+        <v>471</v>
       </c>
       <c r="I40" t="n">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="J40" t="n">
-        <v>537</v>
+        <v>472</v>
       </c>
       <c r="K40" t="n">
-        <v>498</v>
+        <v>437</v>
       </c>
       <c r="L40" t="n">
-        <v>520.1</v>
+        <v>471.2</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
+        <v>498</v>
+      </c>
+      <c r="C41" t="n">
+        <v>566</v>
+      </c>
+      <c r="D41" t="n">
+        <v>490</v>
+      </c>
+      <c r="E41" t="n">
         <v>506</v>
       </c>
-      <c r="C41" t="n">
-        <v>553</v>
-      </c>
-      <c r="D41" t="n">
-        <v>572</v>
-      </c>
-      <c r="E41" t="n">
-        <v>480</v>
-      </c>
       <c r="F41" t="n">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="G41" t="n">
-        <v>542</v>
+        <v>510</v>
       </c>
       <c r="H41" t="n">
-        <v>510</v>
+        <v>485</v>
       </c>
       <c r="I41" t="n">
+        <v>555</v>
+      </c>
+      <c r="J41" t="n">
         <v>488</v>
       </c>
-      <c r="J41" t="n">
-        <v>520</v>
-      </c>
       <c r="K41" t="n">
-        <v>633</v>
+        <v>514</v>
       </c>
       <c r="L41" t="n">
-        <v>531.3</v>
+        <v>516.2</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>536</v>
+        <v>493</v>
       </c>
       <c r="C42" t="n">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="D42" t="n">
-        <v>517</v>
+        <v>451</v>
       </c>
       <c r="E42" t="n">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="F42" t="n">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="G42" t="n">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="H42" t="n">
-        <v>505</v>
+        <v>475</v>
       </c>
       <c r="I42" t="n">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="J42" t="n">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="K42" t="n">
-        <v>476</v>
+        <v>434</v>
       </c>
       <c r="L42" t="n">
-        <v>493.6</v>
+        <v>475.1</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>497</v>
+        <v>557</v>
       </c>
       <c r="C43" t="n">
-        <v>495</v>
+        <v>520</v>
       </c>
       <c r="D43" t="n">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="E43" t="n">
-        <v>532</v>
+        <v>488</v>
       </c>
       <c r="F43" t="n">
+        <v>512</v>
+      </c>
+      <c r="G43" t="n">
+        <v>523</v>
+      </c>
+      <c r="H43" t="n">
+        <v>464</v>
+      </c>
+      <c r="I43" t="n">
         <v>490</v>
       </c>
-      <c r="G43" t="n">
-        <v>503</v>
-      </c>
-      <c r="H43" t="n">
-        <v>425</v>
-      </c>
-      <c r="I43" t="n">
-        <v>520</v>
-      </c>
       <c r="J43" t="n">
-        <v>531</v>
+        <v>508</v>
       </c>
       <c r="K43" t="n">
-        <v>466</v>
+        <v>557</v>
       </c>
       <c r="L43" t="n">
-        <v>498.5</v>
+        <v>511.8</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>519</v>
+        <v>443</v>
       </c>
       <c r="C44" t="n">
-        <v>514</v>
+        <v>462</v>
       </c>
       <c r="D44" t="n">
-        <v>526</v>
+        <v>480</v>
       </c>
       <c r="E44" t="n">
-        <v>501</v>
+        <v>433</v>
       </c>
       <c r="F44" t="n">
-        <v>538</v>
+        <v>456</v>
       </c>
       <c r="G44" t="n">
-        <v>599</v>
+        <v>425</v>
       </c>
       <c r="H44" t="n">
-        <v>520</v>
+        <v>454</v>
       </c>
       <c r="I44" t="n">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="J44" t="n">
-        <v>448</v>
+        <v>507</v>
       </c>
       <c r="K44" t="n">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="L44" t="n">
-        <v>507.9</v>
+        <v>455.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>546</v>
+        <v>470</v>
       </c>
       <c r="C45" t="n">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D45" t="n">
-        <v>578</v>
+        <v>513</v>
       </c>
       <c r="E45" t="n">
-        <v>481</v>
+        <v>529</v>
       </c>
       <c r="F45" t="n">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="G45" t="n">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="H45" t="n">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="I45" t="n">
-        <v>582</v>
+        <v>565</v>
       </c>
       <c r="J45" t="n">
-        <v>531</v>
+        <v>451</v>
       </c>
       <c r="K45" t="n">
-        <v>508</v>
+        <v>462</v>
       </c>
       <c r="L45" t="n">
-        <v>521.9</v>
+        <v>498.4</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>458</v>
+        <v>423</v>
       </c>
       <c r="C46" t="n">
-        <v>467</v>
+        <v>407</v>
       </c>
       <c r="D46" t="n">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="E46" t="n">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="F46" t="n">
+        <v>446</v>
+      </c>
+      <c r="G46" t="n">
         <v>430</v>
       </c>
-      <c r="G46" t="n">
-        <v>428</v>
-      </c>
       <c r="H46" t="n">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="I46" t="n">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="J46" t="n">
-        <v>545</v>
+        <v>465</v>
       </c>
       <c r="K46" t="n">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="L46" t="n">
-        <v>435.8</v>
+        <v>421.4</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C47" t="n">
-        <v>674</v>
+        <v>568</v>
       </c>
       <c r="D47" t="n">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="E47" t="n">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="F47" t="n">
-        <v>624</v>
+        <v>582</v>
       </c>
       <c r="G47" t="n">
-        <v>596</v>
+        <v>530</v>
       </c>
       <c r="H47" t="n">
-        <v>554</v>
+        <v>607</v>
       </c>
       <c r="I47" t="n">
-        <v>523</v>
+        <v>458</v>
       </c>
       <c r="J47" t="n">
-        <v>616</v>
+        <v>521</v>
       </c>
       <c r="K47" t="n">
-        <v>661</v>
+        <v>629</v>
       </c>
       <c r="L47" t="n">
-        <v>590.3</v>
+        <v>553.8</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>559</v>
+        <v>509</v>
       </c>
       <c r="C48" t="n">
+        <v>536</v>
+      </c>
+      <c r="D48" t="n">
+        <v>566</v>
+      </c>
+      <c r="E48" t="n">
+        <v>528</v>
+      </c>
+      <c r="F48" t="n">
+        <v>513</v>
+      </c>
+      <c r="G48" t="n">
+        <v>538</v>
+      </c>
+      <c r="H48" t="n">
+        <v>564</v>
+      </c>
+      <c r="I48" t="n">
+        <v>502</v>
+      </c>
+      <c r="J48" t="n">
+        <v>538</v>
+      </c>
+      <c r="K48" t="n">
         <v>549</v>
       </c>
-      <c r="D48" t="n">
-        <v>558</v>
-      </c>
-      <c r="E48" t="n">
-        <v>482</v>
-      </c>
-      <c r="F48" t="n">
-        <v>527</v>
-      </c>
-      <c r="G48" t="n">
-        <v>523</v>
-      </c>
-      <c r="H48" t="n">
-        <v>567</v>
-      </c>
-      <c r="I48" t="n">
-        <v>504</v>
-      </c>
-      <c r="J48" t="n">
-        <v>678</v>
-      </c>
-      <c r="K48" t="n">
-        <v>556</v>
-      </c>
       <c r="L48" t="n">
-        <v>550.3</v>
+        <v>534.3</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>517</v>
+        <v>488</v>
       </c>
       <c r="C49" t="n">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="D49" t="n">
-        <v>536</v>
+        <v>395</v>
       </c>
       <c r="E49" t="n">
-        <v>540</v>
+        <v>483</v>
       </c>
       <c r="F49" t="n">
-        <v>444</v>
+        <v>502</v>
       </c>
       <c r="G49" t="n">
-        <v>564</v>
+        <v>435</v>
       </c>
       <c r="H49" t="n">
-        <v>501</v>
+        <v>534</v>
       </c>
       <c r="I49" t="n">
-        <v>504</v>
+        <v>421</v>
       </c>
       <c r="J49" t="n">
-        <v>491</v>
+        <v>466</v>
       </c>
       <c r="K49" t="n">
-        <v>510</v>
+        <v>551</v>
       </c>
       <c r="L49" t="n">
-        <v>507.8</v>
+        <v>478.7</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>495</v>
+        <v>447</v>
       </c>
       <c r="C50" t="n">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="D50" t="n">
-        <v>408</v>
+        <v>442</v>
       </c>
       <c r="E50" t="n">
-        <v>561</v>
+        <v>434</v>
       </c>
       <c r="F50" t="n">
         <v>524</v>
       </c>
       <c r="G50" t="n">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="H50" t="n">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="I50" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="J50" t="n">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="K50" t="n">
-        <v>546</v>
+        <v>389</v>
       </c>
       <c r="L50" t="n">
-        <v>484.6</v>
+        <v>445.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>500</v>
+        <v>427</v>
       </c>
       <c r="C51" t="n">
-        <v>420</v>
+        <v>392</v>
       </c>
       <c r="D51" t="n">
-        <v>477</v>
+        <v>392</v>
       </c>
       <c r="E51" t="n">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="F51" t="n">
-        <v>505</v>
+        <v>460</v>
       </c>
       <c r="G51" t="n">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="H51" t="n">
-        <v>510</v>
+        <v>433</v>
       </c>
       <c r="I51" t="n">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="J51" t="n">
-        <v>522</v>
+        <v>480</v>
       </c>
       <c r="K51" t="n">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="L51" t="n">
-        <v>475.5</v>
+        <v>438.1</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>507.64</v>
+        <v>478.44</v>
       </c>
       <c r="C52" t="n">
-        <v>521.84</v>
+        <v>485.9</v>
       </c>
       <c r="D52" t="n">
-        <v>506.58</v>
+        <v>478.7</v>
       </c>
       <c r="E52" t="n">
-        <v>516.9400000000001</v>
+        <v>491.8</v>
       </c>
       <c r="F52" t="n">
-        <v>495.9</v>
+        <v>485.18</v>
       </c>
       <c r="G52" t="n">
-        <v>502.56</v>
+        <v>480.44</v>
       </c>
       <c r="H52" t="n">
-        <v>510.38</v>
+        <v>490.46</v>
       </c>
       <c r="I52" t="n">
-        <v>501.98</v>
+        <v>483.86</v>
       </c>
       <c r="J52" t="n">
-        <v>517.2</v>
+        <v>491.36</v>
       </c>
       <c r="K52" t="n">
-        <v>502.04</v>
+        <v>490.16</v>
       </c>
       <c r="L52" t="n">
-        <v>508.306</v>
+        <v>485.63</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.217054128646851</v>
+        <v>2.519254207611084</v>
       </c>
       <c r="C2" t="n">
-        <v>2.199373483657837</v>
+        <v>2.309548616409302</v>
       </c>
       <c r="D2" t="n">
-        <v>2.400871276855469</v>
+        <v>2.294620037078857</v>
       </c>
       <c r="E2" t="n">
-        <v>2.478976011276245</v>
+        <v>2.267466068267822</v>
       </c>
       <c r="F2" t="n">
-        <v>2.449427366256714</v>
+        <v>2.349735021591187</v>
       </c>
       <c r="G2" t="n">
-        <v>2.118147373199463</v>
+        <v>2.448456764221191</v>
       </c>
       <c r="H2" t="n">
-        <v>2.282094717025757</v>
+        <v>2.307303905487061</v>
       </c>
       <c r="I2" t="n">
-        <v>2.337116003036499</v>
+        <v>2.231709241867065</v>
       </c>
       <c r="J2" t="n">
-        <v>2.363347291946411</v>
+        <v>2.197672367095947</v>
       </c>
       <c r="K2" t="n">
-        <v>2.416474103927612</v>
+        <v>2.393130540847778</v>
       </c>
       <c r="L2" t="n">
-        <v>2.326288175582886</v>
+        <v>2.331889677047729</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.318028450012207</v>
+        <v>2.619414091110229</v>
       </c>
       <c r="C3" t="n">
-        <v>2.485675811767578</v>
+        <v>2.495229005813599</v>
       </c>
       <c r="D3" t="n">
-        <v>2.370450019836426</v>
+        <v>2.570941686630249</v>
       </c>
       <c r="E3" t="n">
-        <v>2.585491418838501</v>
+        <v>2.879058599472046</v>
       </c>
       <c r="F3" t="n">
-        <v>2.380989789962769</v>
+        <v>2.925427198410034</v>
       </c>
       <c r="G3" t="n">
-        <v>2.183956623077393</v>
+        <v>2.519955635070801</v>
       </c>
       <c r="H3" t="n">
-        <v>2.467624664306641</v>
+        <v>2.654903888702393</v>
       </c>
       <c r="I3" t="n">
-        <v>2.77849817276001</v>
+        <v>2.511259794235229</v>
       </c>
       <c r="J3" t="n">
-        <v>2.382786750793457</v>
+        <v>2.714287519454956</v>
       </c>
       <c r="K3" t="n">
-        <v>2.690992593765259</v>
+        <v>2.716866970062256</v>
       </c>
       <c r="L3" t="n">
-        <v>2.464449429512024</v>
+        <v>2.660734438896179</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.424097776412964</v>
+        <v>2.698747396469116</v>
       </c>
       <c r="C4" t="n">
-        <v>2.579060316085815</v>
+        <v>2.59636378288269</v>
       </c>
       <c r="D4" t="n">
-        <v>3.576579332351685</v>
+        <v>2.413502931594849</v>
       </c>
       <c r="E4" t="n">
-        <v>2.802254438400269</v>
+        <v>3.345667123794556</v>
       </c>
       <c r="F4" t="n">
-        <v>2.557968139648438</v>
+        <v>4.073050260543823</v>
       </c>
       <c r="G4" t="n">
-        <v>2.762660264968872</v>
+        <v>2.562927007675171</v>
       </c>
       <c r="H4" t="n">
-        <v>2.310712099075317</v>
+        <v>2.574350357055664</v>
       </c>
       <c r="I4" t="n">
-        <v>2.407104969024658</v>
+        <v>2.327865600585938</v>
       </c>
       <c r="J4" t="n">
-        <v>2.521925687789917</v>
+        <v>2.404569864273071</v>
       </c>
       <c r="K4" t="n">
-        <v>2.556034803390503</v>
+        <v>2.503917932510376</v>
       </c>
       <c r="L4" t="n">
-        <v>2.649839782714844</v>
+        <v>2.750096225738525</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2.270795822143555</v>
+        <v>2.080435991287231</v>
       </c>
       <c r="C5" t="n">
-        <v>2.112496376037598</v>
+        <v>2.112350940704346</v>
       </c>
       <c r="D5" t="n">
-        <v>2.353673696517944</v>
+        <v>2.228041887283325</v>
       </c>
       <c r="E5" t="n">
-        <v>2.323674917221069</v>
+        <v>2.267934083938599</v>
       </c>
       <c r="F5" t="n">
-        <v>2.246284961700439</v>
+        <v>2.167204141616821</v>
       </c>
       <c r="G5" t="n">
-        <v>2.331886768341064</v>
+        <v>2.164212465286255</v>
       </c>
       <c r="H5" t="n">
-        <v>2.349736213684082</v>
+        <v>2.30583381652832</v>
       </c>
       <c r="I5" t="n">
-        <v>2.190503835678101</v>
+        <v>2.354703664779663</v>
       </c>
       <c r="J5" t="n">
-        <v>2.484317064285278</v>
+        <v>2.433491468429565</v>
       </c>
       <c r="K5" t="n">
-        <v>2.150112867355347</v>
+        <v>2.217070817947388</v>
       </c>
       <c r="L5" t="n">
-        <v>2.281348252296448</v>
+        <v>2.233127927780151</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>2.07518196105957</v>
+        <v>1.896926879882812</v>
       </c>
       <c r="C6" t="n">
-        <v>2.221533536911011</v>
+        <v>2.227044582366943</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067784786224365</v>
+        <v>2.426043033599854</v>
       </c>
       <c r="E6" t="n">
-        <v>2.241477251052856</v>
+        <v>2.001837730407715</v>
       </c>
       <c r="F6" t="n">
-        <v>2.291139125823975</v>
+        <v>1.910932302474976</v>
       </c>
       <c r="G6" t="n">
-        <v>2.214041948318481</v>
+        <v>1.89719557762146</v>
       </c>
       <c r="H6" t="n">
-        <v>2.121777296066284</v>
+        <v>2.025617837905884</v>
       </c>
       <c r="I6" t="n">
-        <v>2.37445855140686</v>
+        <v>2.477060794830322</v>
       </c>
       <c r="J6" t="n">
-        <v>2.157055616378784</v>
+        <v>2.210282802581787</v>
       </c>
       <c r="K6" t="n">
-        <v>1.959551572799683</v>
+        <v>2.229483604431152</v>
       </c>
       <c r="L6" t="n">
-        <v>2.172400164604187</v>
+        <v>2.13024251461029</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.510421752929688</v>
+        <v>2.444463491439819</v>
       </c>
       <c r="C7" t="n">
-        <v>2.366168975830078</v>
+        <v>2.505300045013428</v>
       </c>
       <c r="D7" t="n">
-        <v>2.536388158798218</v>
+        <v>2.32278847694397</v>
       </c>
       <c r="E7" t="n">
-        <v>2.372778415679932</v>
+        <v>2.353135824203491</v>
       </c>
       <c r="F7" t="n">
-        <v>2.338363409042358</v>
+        <v>2.635984182357788</v>
       </c>
       <c r="G7" t="n">
-        <v>2.465585708618164</v>
+        <v>2.49799370765686</v>
       </c>
       <c r="H7" t="n">
-        <v>2.426955699920654</v>
+        <v>2.377667427062988</v>
       </c>
       <c r="I7" t="n">
-        <v>2.43931245803833</v>
+        <v>2.412336111068726</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4996178150177</v>
+        <v>2.407590866088867</v>
       </c>
       <c r="K7" t="n">
-        <v>2.389989852905273</v>
+        <v>2.328091144561768</v>
       </c>
       <c r="L7" t="n">
-        <v>2.43455822467804</v>
+        <v>2.42853512763977</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.574512958526611</v>
+        <v>2.434489011764526</v>
       </c>
       <c r="C8" t="n">
-        <v>2.52575945854187</v>
+        <v>2.496325254440308</v>
       </c>
       <c r="D8" t="n">
-        <v>2.452808618545532</v>
+        <v>2.231034278869629</v>
       </c>
       <c r="E8" t="n">
-        <v>2.282539844512939</v>
+        <v>2.812478303909302</v>
       </c>
       <c r="F8" t="n">
-        <v>2.448350191116333</v>
+        <v>2.551177978515625</v>
       </c>
       <c r="G8" t="n">
-        <v>2.359153747558594</v>
+        <v>2.291784763336182</v>
       </c>
       <c r="H8" t="n">
-        <v>2.405742883682251</v>
+        <v>2.308148860931396</v>
       </c>
       <c r="I8" t="n">
-        <v>2.578978776931763</v>
+        <v>2.317496061325073</v>
       </c>
       <c r="J8" t="n">
-        <v>2.757825374603271</v>
+        <v>2.558196783065796</v>
       </c>
       <c r="K8" t="n">
-        <v>2.590731620788574</v>
+        <v>2.314809322357178</v>
       </c>
       <c r="L8" t="n">
-        <v>2.497640347480774</v>
+        <v>2.431594061851501</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.20701789855957</v>
+        <v>2.264102220535278</v>
       </c>
       <c r="C9" t="n">
-        <v>2.427042484283447</v>
+        <v>2.210124969482422</v>
       </c>
       <c r="D9" t="n">
-        <v>2.289514541625977</v>
+        <v>2.241007089614868</v>
       </c>
       <c r="E9" t="n">
-        <v>2.388327836990356</v>
+        <v>2.288863658905029</v>
       </c>
       <c r="F9" t="n">
-        <v>2.395874977111816</v>
+        <v>2.232062101364136</v>
       </c>
       <c r="G9" t="n">
-        <v>2.461589574813843</v>
+        <v>2.245993852615356</v>
       </c>
       <c r="H9" t="n">
-        <v>2.287757873535156</v>
+        <v>2.304836750030518</v>
       </c>
       <c r="I9" t="n">
-        <v>2.305808305740356</v>
+        <v>2.297624588012695</v>
       </c>
       <c r="J9" t="n">
-        <v>2.312184810638428</v>
+        <v>2.279935836791992</v>
       </c>
       <c r="K9" t="n">
-        <v>2.354061126708984</v>
+        <v>2.213081836700439</v>
       </c>
       <c r="L9" t="n">
-        <v>2.342917943000793</v>
+        <v>2.257763290405273</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.293943405151367</v>
+        <v>2.217056751251221</v>
       </c>
       <c r="C10" t="n">
-        <v>2.529624700546265</v>
+        <v>2.249983072280884</v>
       </c>
       <c r="D10" t="n">
-        <v>2.382758140563965</v>
+        <v>2.565140008926392</v>
       </c>
       <c r="E10" t="n">
-        <v>2.455722093582153</v>
+        <v>2.370660066604614</v>
       </c>
       <c r="F10" t="n">
-        <v>2.429524660110474</v>
+        <v>2.308538436889648</v>
       </c>
       <c r="G10" t="n">
-        <v>2.205983400344849</v>
+        <v>2.32880425453186</v>
       </c>
       <c r="H10" t="n">
-        <v>2.31505274772644</v>
+        <v>2.233028173446655</v>
       </c>
       <c r="I10" t="n">
-        <v>2.377694368362427</v>
+        <v>2.528238296508789</v>
       </c>
       <c r="J10" t="n">
-        <v>2.481120109558105</v>
+        <v>2.213297843933105</v>
       </c>
       <c r="K10" t="n">
-        <v>2.296391010284424</v>
+        <v>2.524287700653076</v>
       </c>
       <c r="L10" t="n">
-        <v>2.376781463623047</v>
+        <v>2.353903460502624</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>2.177366256713867</v>
+        <v>2.114345788955688</v>
       </c>
       <c r="C11" t="n">
-        <v>2.017510890960693</v>
+        <v>2.013291120529175</v>
       </c>
       <c r="D11" t="n">
-        <v>2.119927883148193</v>
+        <v>1.89336895942688</v>
       </c>
       <c r="E11" t="n">
-        <v>2.079944849014282</v>
+        <v>1.890942573547363</v>
       </c>
       <c r="F11" t="n">
-        <v>2.255651712417603</v>
+        <v>2.004639863967896</v>
       </c>
       <c r="G11" t="n">
-        <v>2.099700689315796</v>
+        <v>1.959758281707764</v>
       </c>
       <c r="H11" t="n">
-        <v>1.983287572860718</v>
+        <v>1.977711200714111</v>
       </c>
       <c r="I11" t="n">
-        <v>2.021689653396606</v>
+        <v>2.047524452209473</v>
       </c>
       <c r="J11" t="n">
-        <v>2.138325452804565</v>
+        <v>1.892653942108154</v>
       </c>
       <c r="K11" t="n">
-        <v>2.082000494003296</v>
+        <v>1.94582986831665</v>
       </c>
       <c r="L11" t="n">
-        <v>2.097540545463562</v>
+        <v>1.974006605148315</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.275407791137695</v>
+        <v>2.22604775428772</v>
       </c>
       <c r="C12" t="n">
-        <v>2.25455117225647</v>
+        <v>2.271924018859863</v>
       </c>
       <c r="D12" t="n">
-        <v>2.11758279800415</v>
+        <v>2.208095788955688</v>
       </c>
       <c r="E12" t="n">
-        <v>2.539402723312378</v>
+        <v>2.672971963882446</v>
       </c>
       <c r="F12" t="n">
-        <v>2.412510871887207</v>
+        <v>2.492336511611938</v>
       </c>
       <c r="G12" t="n">
-        <v>2.33499813079834</v>
+        <v>2.388647317886353</v>
       </c>
       <c r="H12" t="n">
-        <v>2.277636051177979</v>
+        <v>2.194133043289185</v>
       </c>
       <c r="I12" t="n">
-        <v>2.38306999206543</v>
+        <v>2.27669358253479</v>
       </c>
       <c r="J12" t="n">
-        <v>2.29632568359375</v>
+        <v>2.197154998779297</v>
       </c>
       <c r="K12" t="n">
-        <v>19.36044263839722</v>
+        <v>2.316804647445679</v>
       </c>
       <c r="L12" t="n">
-        <v>4.025192785263061</v>
+        <v>2.324480962753296</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.619757652282715</v>
+        <v>2.224595785140991</v>
       </c>
       <c r="C13" t="n">
-        <v>2.485628366470337</v>
+        <v>2.397644281387329</v>
       </c>
       <c r="D13" t="n">
-        <v>2.505422592163086</v>
+        <v>2.484405755996704</v>
       </c>
       <c r="E13" t="n">
-        <v>2.510168075561523</v>
+        <v>2.645585060119629</v>
       </c>
       <c r="F13" t="n">
-        <v>2.307532548904419</v>
+        <v>2.475423097610474</v>
       </c>
       <c r="G13" t="n">
-        <v>2.275986671447754</v>
+        <v>2.532229661941528</v>
       </c>
       <c r="H13" t="n">
-        <v>2.450387477874756</v>
+        <v>2.631961345672607</v>
       </c>
       <c r="I13" t="n">
-        <v>2.386503934860229</v>
+        <v>2.571561813354492</v>
       </c>
       <c r="J13" t="n">
-        <v>2.252767562866211</v>
+        <v>2.587114572525024</v>
       </c>
       <c r="K13" t="n">
-        <v>2.463729381561279</v>
+        <v>2.36804723739624</v>
       </c>
       <c r="L13" t="n">
-        <v>2.425788426399231</v>
+        <v>2.491856861114502</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.577882766723633</v>
+        <v>2.355700254440308</v>
       </c>
       <c r="C14" t="n">
-        <v>2.522096395492554</v>
+        <v>2.554169893264771</v>
       </c>
       <c r="D14" t="n">
-        <v>2.404494762420654</v>
+        <v>2.658888816833496</v>
       </c>
       <c r="E14" t="n">
-        <v>2.558976650238037</v>
+        <v>2.385935544967651</v>
       </c>
       <c r="F14" t="n">
-        <v>2.465854644775391</v>
+        <v>2.404601812362671</v>
       </c>
       <c r="G14" t="n">
-        <v>2.500493288040161</v>
+        <v>2.92717170715332</v>
       </c>
       <c r="H14" t="n">
-        <v>2.606392383575439</v>
+        <v>2.741523265838623</v>
       </c>
       <c r="I14" t="n">
-        <v>2.624470233917236</v>
+        <v>2.441470623016357</v>
       </c>
       <c r="J14" t="n">
-        <v>2.661617040634155</v>
+        <v>2.246991157531738</v>
       </c>
       <c r="K14" t="n">
-        <v>2.858428955078125</v>
+        <v>2.338745594024658</v>
       </c>
       <c r="L14" t="n">
-        <v>2.578070712089539</v>
+        <v>2.505519866943359</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.555806636810303</v>
+        <v>2.134739875793457</v>
       </c>
       <c r="C15" t="n">
-        <v>2.652833938598633</v>
+        <v>2.162248849868774</v>
       </c>
       <c r="D15" t="n">
-        <v>2.61340069770813</v>
+        <v>2.149251937866211</v>
       </c>
       <c r="E15" t="n">
-        <v>2.888048648834229</v>
+        <v>2.161937236785889</v>
       </c>
       <c r="F15" t="n">
-        <v>2.300068378448486</v>
+        <v>2.100426912307739</v>
       </c>
       <c r="G15" t="n">
-        <v>2.661898851394653</v>
+        <v>2.230036497116089</v>
       </c>
       <c r="H15" t="n">
-        <v>2.520580291748047</v>
+        <v>2.142271280288696</v>
       </c>
       <c r="I15" t="n">
-        <v>3.000986337661743</v>
+        <v>2.251977443695068</v>
       </c>
       <c r="J15" t="n">
-        <v>2.418309688568115</v>
+        <v>2.170196056365967</v>
       </c>
       <c r="K15" t="n">
-        <v>2.395489692687988</v>
+        <v>2.138395071029663</v>
       </c>
       <c r="L15" t="n">
-        <v>2.600742316246033</v>
+        <v>2.164148116111755</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.56769061088562</v>
+        <v>2.418532609939575</v>
       </c>
       <c r="C16" t="n">
-        <v>2.620978116989136</v>
+        <v>2.309823036193848</v>
       </c>
       <c r="D16" t="n">
-        <v>2.372172355651855</v>
+        <v>2.237385034561157</v>
       </c>
       <c r="E16" t="n">
-        <v>2.464430809020996</v>
+        <v>2.333760023117065</v>
       </c>
       <c r="F16" t="n">
-        <v>2.401964664459229</v>
+        <v>2.226047039031982</v>
       </c>
       <c r="G16" t="n">
-        <v>2.540225267410278</v>
+        <v>2.239306449890137</v>
       </c>
       <c r="H16" t="n">
-        <v>2.476323366165161</v>
+        <v>2.196871757507324</v>
       </c>
       <c r="I16" t="n">
-        <v>2.597878456115723</v>
+        <v>2.367715358734131</v>
       </c>
       <c r="J16" t="n">
-        <v>2.48823881149292</v>
+        <v>2.315038204193115</v>
       </c>
       <c r="K16" t="n">
-        <v>2.421948909759521</v>
+        <v>2.12958550453186</v>
       </c>
       <c r="L16" t="n">
-        <v>2.495185136795044</v>
+        <v>2.277406501770019</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.517193555831909</v>
+        <v>2.155236005783081</v>
       </c>
       <c r="C17" t="n">
-        <v>2.703443050384521</v>
+        <v>2.382153987884521</v>
       </c>
       <c r="D17" t="n">
-        <v>2.555222272872925</v>
+        <v>2.340771675109863</v>
       </c>
       <c r="E17" t="n">
-        <v>2.491815805435181</v>
+        <v>2.120861053466797</v>
       </c>
       <c r="F17" t="n">
-        <v>2.567652225494385</v>
+        <v>2.362714529037476</v>
       </c>
       <c r="G17" t="n">
-        <v>2.408888339996338</v>
+        <v>2.262948036193848</v>
       </c>
       <c r="H17" t="n">
-        <v>2.523974657058716</v>
+        <v>2.210418939590454</v>
       </c>
       <c r="I17" t="n">
-        <v>2.296078205108643</v>
+        <v>2.221089839935303</v>
       </c>
       <c r="J17" t="n">
-        <v>2.782145500183105</v>
+        <v>2.148255586624146</v>
       </c>
       <c r="K17" t="n">
-        <v>2.581451892852783</v>
+        <v>2.635950326919556</v>
       </c>
       <c r="L17" t="n">
-        <v>2.542786550521851</v>
+        <v>2.284039998054504</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>3.114456176757812</v>
+        <v>2.566137552261353</v>
       </c>
       <c r="C18" t="n">
-        <v>3.33344578742981</v>
+        <v>2.618619918823242</v>
       </c>
       <c r="D18" t="n">
-        <v>3.17042088508606</v>
+        <v>2.618029117584229</v>
       </c>
       <c r="E18" t="n">
-        <v>2.76354193687439</v>
+        <v>2.659524917602539</v>
       </c>
       <c r="F18" t="n">
-        <v>2.775030612945557</v>
+        <v>2.572154760360718</v>
       </c>
       <c r="G18" t="n">
-        <v>2.491849422454834</v>
+        <v>2.616004228591919</v>
       </c>
       <c r="H18" t="n">
-        <v>2.656705856323242</v>
+        <v>2.883289098739624</v>
       </c>
       <c r="I18" t="n">
-        <v>2.932572841644287</v>
+        <v>2.561530828475952</v>
       </c>
       <c r="J18" t="n">
-        <v>2.598051786422729</v>
+        <v>2.514328241348267</v>
       </c>
       <c r="K18" t="n">
-        <v>2.886369943618774</v>
+        <v>2.656895160675049</v>
       </c>
       <c r="L18" t="n">
-        <v>2.872244524955749</v>
+        <v>2.626651382446289</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.464051961898804</v>
+        <v>2.182164192199707</v>
       </c>
       <c r="C19" t="n">
-        <v>2.764450788497925</v>
+        <v>2.599048614501953</v>
       </c>
       <c r="D19" t="n">
-        <v>2.667799711227417</v>
+        <v>2.200115919113159</v>
       </c>
       <c r="E19" t="n">
-        <v>2.817276954650879</v>
+        <v>2.203108549118042</v>
       </c>
       <c r="F19" t="n">
-        <v>2.565587759017944</v>
+        <v>2.112934589385986</v>
       </c>
       <c r="G19" t="n">
-        <v>2.549243211746216</v>
+        <v>2.426543235778809</v>
       </c>
       <c r="H19" t="n">
-        <v>2.732606172561646</v>
+        <v>2.332761526107788</v>
       </c>
       <c r="I19" t="n">
-        <v>2.572777271270752</v>
+        <v>2.322561502456665</v>
       </c>
       <c r="J19" t="n">
-        <v>2.448714733123779</v>
+        <v>2.289390325546265</v>
       </c>
       <c r="K19" t="n">
-        <v>2.581925868988037</v>
+        <v>2.414649963378906</v>
       </c>
       <c r="L19" t="n">
-        <v>2.61644344329834</v>
+        <v>2.308327841758728</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.60881781578064</v>
+        <v>2.261540651321411</v>
       </c>
       <c r="C20" t="n">
-        <v>2.587791919708252</v>
+        <v>2.579135656356812</v>
       </c>
       <c r="D20" t="n">
-        <v>2.692463636398315</v>
+        <v>2.280900001525879</v>
       </c>
       <c r="E20" t="n">
-        <v>2.071480989456177</v>
+        <v>2.546191215515137</v>
       </c>
       <c r="F20" t="n">
-        <v>2.167512655258179</v>
+        <v>2.67384934425354</v>
       </c>
       <c r="G20" t="n">
-        <v>2.482813119888306</v>
+        <v>2.365791320800781</v>
       </c>
       <c r="H20" t="n">
-        <v>2.420990228652954</v>
+        <v>2.601044178009033</v>
       </c>
       <c r="I20" t="n">
-        <v>2.659552812576294</v>
+        <v>2.471390724182129</v>
       </c>
       <c r="J20" t="n">
-        <v>2.56074857711792</v>
+        <v>2.572666883468628</v>
       </c>
       <c r="K20" t="n">
-        <v>2.344020843505859</v>
+        <v>2.521288633346558</v>
       </c>
       <c r="L20" t="n">
-        <v>2.45961925983429</v>
+        <v>2.487379860877991</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.442801952362061</v>
+        <v>2.709043502807617</v>
       </c>
       <c r="C21" t="n">
-        <v>2.554685592651367</v>
+        <v>2.381805181503296</v>
       </c>
       <c r="D21" t="n">
-        <v>2.431922912597656</v>
+        <v>2.488345623016357</v>
       </c>
       <c r="E21" t="n">
-        <v>2.831020355224609</v>
+        <v>2.467856645584106</v>
       </c>
       <c r="F21" t="n">
-        <v>2.267434358596802</v>
+        <v>2.383625984191895</v>
       </c>
       <c r="G21" t="n">
-        <v>2.458685636520386</v>
+        <v>2.479451179504395</v>
       </c>
       <c r="H21" t="n">
-        <v>2.319478750228882</v>
+        <v>2.577152252197266</v>
       </c>
       <c r="I21" t="n">
-        <v>2.598067998886108</v>
+        <v>2.386618137359619</v>
       </c>
       <c r="J21" t="n">
-        <v>2.289990901947021</v>
+        <v>2.340213060379028</v>
       </c>
       <c r="K21" t="n">
-        <v>2.217878580093384</v>
+        <v>2.403605937957764</v>
       </c>
       <c r="L21" t="n">
-        <v>2.441196703910828</v>
+        <v>2.461771750450134</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.346536874771118</v>
+        <v>2.278343677520752</v>
       </c>
       <c r="C22" t="n">
-        <v>2.521491050720215</v>
+        <v>2.22213888168335</v>
       </c>
       <c r="D22" t="n">
-        <v>2.245278835296631</v>
+        <v>2.12631368637085</v>
       </c>
       <c r="E22" t="n">
-        <v>2.223306894302368</v>
+        <v>2.155236482620239</v>
       </c>
       <c r="F22" t="n">
-        <v>2.186534404754639</v>
+        <v>2.189145803451538</v>
       </c>
       <c r="G22" t="n">
-        <v>2.378844738006592</v>
+        <v>2.272922277450562</v>
       </c>
       <c r="H22" t="n">
-        <v>2.315600156784058</v>
+        <v>2.223618984222412</v>
       </c>
       <c r="I22" t="n">
-        <v>2.365628242492676</v>
+        <v>2.150277137756348</v>
       </c>
       <c r="J22" t="n">
-        <v>2.541875123977661</v>
+        <v>2.26793646812439</v>
       </c>
       <c r="K22" t="n">
-        <v>2.470303535461426</v>
+        <v>2.244167804718018</v>
       </c>
       <c r="L22" t="n">
-        <v>2.359539985656738</v>
+        <v>2.213010120391846</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>2.022091150283813</v>
+        <v>2.100382566452026</v>
       </c>
       <c r="C23" t="n">
-        <v>1.979888677597046</v>
+        <v>2.036553621292114</v>
       </c>
       <c r="D23" t="n">
-        <v>2.168644189834595</v>
+        <v>2.069465398788452</v>
       </c>
       <c r="E23" t="n">
-        <v>1.88784122467041</v>
+        <v>2.025970935821533</v>
       </c>
       <c r="F23" t="n">
-        <v>2.02350378036499</v>
+        <v>2.14930248260498</v>
       </c>
       <c r="G23" t="n">
-        <v>2.115596294403076</v>
+        <v>1.977710962295532</v>
       </c>
       <c r="H23" t="n">
-        <v>1.952072620391846</v>
+        <v>2.226046800613403</v>
       </c>
       <c r="I23" t="n">
-        <v>2.18177318572998</v>
+        <v>2.14925217628479</v>
       </c>
       <c r="J23" t="n">
-        <v>2.054195880889893</v>
+        <v>2.10537052154541</v>
       </c>
       <c r="K23" t="n">
-        <v>2.083030462265015</v>
+        <v>2.114470720291138</v>
       </c>
       <c r="L23" t="n">
-        <v>2.046863746643067</v>
+        <v>2.095452618598938</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>2.079946994781494</v>
+        <v>2.088415145874023</v>
       </c>
       <c r="C24" t="n">
-        <v>2.320615530014038</v>
+        <v>2.358878135681152</v>
       </c>
       <c r="D24" t="n">
-        <v>2.120178461074829</v>
+        <v>2.025623083114624</v>
       </c>
       <c r="E24" t="n">
-        <v>2.045791625976562</v>
+        <v>2.087671279907227</v>
       </c>
       <c r="F24" t="n">
-        <v>2.159586906433105</v>
+        <v>1.966768264770508</v>
       </c>
       <c r="G24" t="n">
-        <v>2.220158100128174</v>
+        <v>2.125316858291626</v>
       </c>
       <c r="H24" t="n">
-        <v>2.162232637405396</v>
+        <v>2.004360675811768</v>
       </c>
       <c r="I24" t="n">
-        <v>2.230709075927734</v>
+        <v>2.258797168731689</v>
       </c>
       <c r="J24" t="n">
-        <v>2.322835445404053</v>
+        <v>2.586767435073853</v>
       </c>
       <c r="K24" t="n">
-        <v>2.110604286193848</v>
+        <v>2.395741701126099</v>
       </c>
       <c r="L24" t="n">
-        <v>2.177265906333923</v>
+        <v>2.189833974838257</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.433471202850342</v>
+        <v>2.406563997268677</v>
       </c>
       <c r="C25" t="n">
-        <v>2.348996639251709</v>
+        <v>2.307498931884766</v>
       </c>
       <c r="D25" t="n">
-        <v>2.297076225280762</v>
+        <v>2.155388116836548</v>
       </c>
       <c r="E25" t="n">
-        <v>2.318572521209717</v>
+        <v>2.45384407043457</v>
       </c>
       <c r="F25" t="n">
-        <v>2.409871578216553</v>
+        <v>2.303966999053955</v>
       </c>
       <c r="G25" t="n">
-        <v>2.247884511947632</v>
+        <v>2.227044105529785</v>
       </c>
       <c r="H25" t="n">
-        <v>2.355056285858154</v>
+        <v>2.167477130889893</v>
       </c>
       <c r="I25" t="n">
-        <v>2.264050722122192</v>
+        <v>2.000680208206177</v>
       </c>
       <c r="J25" t="n">
-        <v>2.372244596481323</v>
+        <v>2.302502393722534</v>
       </c>
       <c r="K25" t="n">
-        <v>2.318127155303955</v>
+        <v>2.392601251602173</v>
       </c>
       <c r="L25" t="n">
-        <v>2.336535143852234</v>
+        <v>2.271756720542908</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.378729820251465</v>
+        <v>2.127310991287231</v>
       </c>
       <c r="C26" t="n">
-        <v>2.425584554672241</v>
+        <v>2.620406627655029</v>
       </c>
       <c r="D26" t="n">
-        <v>2.492610216140747</v>
+        <v>2.346007585525513</v>
       </c>
       <c r="E26" t="n">
-        <v>2.575215101242065</v>
+        <v>2.493333339691162</v>
       </c>
       <c r="F26" t="n">
-        <v>2.324658632278442</v>
+        <v>2.637944459915161</v>
       </c>
       <c r="G26" t="n">
-        <v>2.400302410125732</v>
+        <v>2.389609575271606</v>
       </c>
       <c r="H26" t="n">
-        <v>2.432334184646606</v>
+        <v>2.420298337936401</v>
       </c>
       <c r="I26" t="n">
-        <v>2.659683227539062</v>
+        <v>2.503954648971558</v>
       </c>
       <c r="J26" t="n">
-        <v>2.433532476425171</v>
+        <v>2.402610301971436</v>
       </c>
       <c r="K26" t="n">
-        <v>2.574967384338379</v>
+        <v>2.489343404769897</v>
       </c>
       <c r="L26" t="n">
-        <v>2.469761800765991</v>
+        <v>2.4430819272995</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2.206724405288696</v>
+        <v>2.092404127120972</v>
       </c>
       <c r="C27" t="n">
-        <v>2.218955039978027</v>
+        <v>2.204106092453003</v>
       </c>
       <c r="D27" t="n">
-        <v>2.281036615371704</v>
+        <v>2.240009069442749</v>
       </c>
       <c r="E27" t="n">
-        <v>2.289487838745117</v>
+        <v>2.203108310699463</v>
       </c>
       <c r="F27" t="n">
-        <v>2.09807276725769</v>
+        <v>2.695756435394287</v>
       </c>
       <c r="G27" t="n">
-        <v>2.513705492019653</v>
+        <v>2.232030630111694</v>
       </c>
       <c r="H27" t="n">
-        <v>2.376006841659546</v>
+        <v>2.24200439453125</v>
       </c>
       <c r="I27" t="n">
-        <v>2.438345670700073</v>
+        <v>2.335753202438354</v>
       </c>
       <c r="J27" t="n">
-        <v>2.259774208068848</v>
+        <v>2.38803243637085</v>
       </c>
       <c r="K27" t="n">
-        <v>2.288755893707275</v>
+        <v>2.419529438018799</v>
       </c>
       <c r="L27" t="n">
-        <v>2.297086477279663</v>
+        <v>2.305273413658142</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.254378080368042</v>
+        <v>2.322787523269653</v>
       </c>
       <c r="C28" t="n">
-        <v>2.134503841400146</v>
+        <v>2.190143346786499</v>
       </c>
       <c r="D28" t="n">
-        <v>2.162109613418579</v>
+        <v>2.239012479782104</v>
       </c>
       <c r="E28" t="n">
-        <v>2.405380487442017</v>
+        <v>2.116673231124878</v>
       </c>
       <c r="F28" t="n">
-        <v>2.145914793014526</v>
+        <v>2.243001937866211</v>
       </c>
       <c r="G28" t="n">
-        <v>2.367308139801025</v>
+        <v>2.504302740097046</v>
       </c>
       <c r="H28" t="n">
-        <v>2.290907621383667</v>
+        <v>2.292352437973022</v>
       </c>
       <c r="I28" t="n">
-        <v>2.221908807754517</v>
+        <v>2.265813589096069</v>
       </c>
       <c r="J28" t="n">
-        <v>2.185203313827515</v>
+        <v>2.12344765663147</v>
       </c>
       <c r="K28" t="n">
-        <v>2.292937517166138</v>
+        <v>2.52026104927063</v>
       </c>
       <c r="L28" t="n">
-        <v>2.246055221557617</v>
+        <v>2.281779599189758</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.270106554031372</v>
+        <v>2.367817878723145</v>
       </c>
       <c r="C29" t="n">
-        <v>2.18818211555481</v>
+        <v>2.410600423812866</v>
       </c>
       <c r="D29" t="n">
-        <v>2.300866842269897</v>
+        <v>2.392601728439331</v>
       </c>
       <c r="E29" t="n">
-        <v>2.258078813552856</v>
+        <v>2.306525707244873</v>
       </c>
       <c r="F29" t="n">
-        <v>2.394211292266846</v>
+        <v>1.992856502532959</v>
       </c>
       <c r="G29" t="n">
-        <v>2.172534704208374</v>
+        <v>2.072041988372803</v>
       </c>
       <c r="H29" t="n">
-        <v>2.168736934661865</v>
+        <v>1.917923450469971</v>
       </c>
       <c r="I29" t="n">
-        <v>2.298063516616821</v>
+        <v>2.236438989639282</v>
       </c>
       <c r="J29" t="n">
-        <v>2.590336084365845</v>
+        <v>2.105038404464722</v>
       </c>
       <c r="K29" t="n">
-        <v>2.334165096282959</v>
+        <v>2.264544248580933</v>
       </c>
       <c r="L29" t="n">
-        <v>2.297528195381164</v>
+        <v>2.206638932228088</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.346825361251831</v>
+        <v>2.070255756378174</v>
       </c>
       <c r="C30" t="n">
-        <v>2.795213937759399</v>
+        <v>2.035598754882812</v>
       </c>
       <c r="D30" t="n">
-        <v>2.437033414840698</v>
+        <v>3.818675994873047</v>
       </c>
       <c r="E30" t="n">
-        <v>2.443055152893066</v>
+        <v>2.949574708938599</v>
       </c>
       <c r="F30" t="n">
-        <v>2.295934200286865</v>
+        <v>2.870090007781982</v>
       </c>
       <c r="G30" t="n">
-        <v>2.593430519104004</v>
+        <v>2.680385589599609</v>
       </c>
       <c r="H30" t="n">
-        <v>2.37096118927002</v>
+        <v>2.683073282241821</v>
       </c>
       <c r="I30" t="n">
-        <v>2.370050430297852</v>
+        <v>2.441105842590332</v>
       </c>
       <c r="J30" t="n">
-        <v>2.283190488815308</v>
+        <v>2.519711256027222</v>
       </c>
       <c r="K30" t="n">
-        <v>2.358795404434204</v>
+        <v>2.189093351364136</v>
       </c>
       <c r="L30" t="n">
-        <v>2.429449009895325</v>
+        <v>2.625756454467774</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.957083940505981</v>
+        <v>1.947323560714722</v>
       </c>
       <c r="C31" t="n">
-        <v>2.050405263900757</v>
+        <v>1.956007242202759</v>
       </c>
       <c r="D31" t="n">
-        <v>1.935316801071167</v>
+        <v>1.956922769546509</v>
       </c>
       <c r="E31" t="n">
-        <v>1.951148509979248</v>
+        <v>1.854935169219971</v>
       </c>
       <c r="F31" t="n">
-        <v>1.943680763244629</v>
+        <v>2.04867696762085</v>
       </c>
       <c r="G31" t="n">
-        <v>2.059170007705688</v>
+        <v>2.063686609268188</v>
       </c>
       <c r="H31" t="n">
-        <v>1.991037607192993</v>
+        <v>2.184428215026855</v>
       </c>
       <c r="I31" t="n">
-        <v>1.984413862228394</v>
+        <v>1.804731607437134</v>
       </c>
       <c r="J31" t="n">
-        <v>1.922382116317749</v>
+        <v>1.981951713562012</v>
       </c>
       <c r="K31" t="n">
-        <v>2.056657075881958</v>
+        <v>2.014654874801636</v>
       </c>
       <c r="L31" t="n">
-        <v>1.985129594802856</v>
+        <v>1.981331872940064</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>2.278804779052734</v>
+        <v>1.995180368423462</v>
       </c>
       <c r="C32" t="n">
-        <v>2.172536611557007</v>
+        <v>2.075672626495361</v>
       </c>
       <c r="D32" t="n">
-        <v>2.321450471878052</v>
+        <v>2.192118167877197</v>
       </c>
       <c r="E32" t="n">
-        <v>2.715826749801636</v>
+        <v>1.974282264709473</v>
       </c>
       <c r="F32" t="n">
-        <v>2.24516224861145</v>
+        <v>1.99957013130188</v>
       </c>
       <c r="G32" t="n">
-        <v>2.421369075775146</v>
+        <v>1.980538129806519</v>
       </c>
       <c r="H32" t="n">
-        <v>2.389409065246582</v>
+        <v>1.983175039291382</v>
       </c>
       <c r="I32" t="n">
-        <v>2.228040218353271</v>
+        <v>2.043608427047729</v>
       </c>
       <c r="J32" t="n">
-        <v>2.253029584884644</v>
+        <v>2.221397876739502</v>
       </c>
       <c r="K32" t="n">
-        <v>2.093672513961792</v>
+        <v>2.040128707885742</v>
       </c>
       <c r="L32" t="n">
-        <v>2.311930131912232</v>
+        <v>2.050567173957825</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.433924198150635</v>
+        <v>2.15494966506958</v>
       </c>
       <c r="C33" t="n">
-        <v>2.286082983016968</v>
+        <v>2.23856520652771</v>
       </c>
       <c r="D33" t="n">
-        <v>2.610051155090332</v>
+        <v>2.2497398853302</v>
       </c>
       <c r="E33" t="n">
-        <v>2.514786958694458</v>
+        <v>2.231462001800537</v>
       </c>
       <c r="F33" t="n">
-        <v>2.410736560821533</v>
+        <v>2.407649278640747</v>
       </c>
       <c r="G33" t="n">
-        <v>2.328021764755249</v>
+        <v>2.203648805618286</v>
       </c>
       <c r="H33" t="n">
-        <v>2.327307224273682</v>
+        <v>2.533457517623901</v>
       </c>
       <c r="I33" t="n">
-        <v>2.382675886154175</v>
+        <v>2.138439893722534</v>
       </c>
       <c r="J33" t="n">
-        <v>2.27508282661438</v>
+        <v>2.088185548782349</v>
       </c>
       <c r="K33" t="n">
-        <v>2.471827268600464</v>
+        <v>2.413252115249634</v>
       </c>
       <c r="L33" t="n">
-        <v>2.404049682617187</v>
+        <v>2.265934991836548</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>2.171572208404541</v>
+        <v>1.889211177825928</v>
       </c>
       <c r="C34" t="n">
-        <v>2.194896936416626</v>
+        <v>2.10614275932312</v>
       </c>
       <c r="D34" t="n">
-        <v>2.022993803024292</v>
+        <v>2.184867858886719</v>
       </c>
       <c r="E34" t="n">
-        <v>2.034804105758667</v>
+        <v>2.120113134384155</v>
       </c>
       <c r="F34" t="n">
-        <v>1.994287252426147</v>
+        <v>1.950750827789307</v>
       </c>
       <c r="G34" t="n">
-        <v>2.08743691444397</v>
+        <v>1.783886432647705</v>
       </c>
       <c r="H34" t="n">
-        <v>2.366514682769775</v>
+        <v>1.748538494110107</v>
       </c>
       <c r="I34" t="n">
-        <v>2.124697685241699</v>
+        <v>1.918798208236694</v>
       </c>
       <c r="J34" t="n">
-        <v>2.211116075515747</v>
+        <v>1.869683265686035</v>
       </c>
       <c r="K34" t="n">
-        <v>1.991027355194092</v>
+        <v>1.971110343933105</v>
       </c>
       <c r="L34" t="n">
-        <v>2.119934701919556</v>
+        <v>1.954310250282288</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.580178260803223</v>
+        <v>2.243176460266113</v>
       </c>
       <c r="C35" t="n">
-        <v>2.565549373626709</v>
+        <v>2.273605108261108</v>
       </c>
       <c r="D35" t="n">
-        <v>2.55951714515686</v>
+        <v>2.209769725799561</v>
       </c>
       <c r="E35" t="n">
-        <v>2.598380327224731</v>
+        <v>2.30444860458374</v>
       </c>
       <c r="F35" t="n">
-        <v>2.672626495361328</v>
+        <v>2.221161842346191</v>
       </c>
       <c r="G35" t="n">
-        <v>2.723897933959961</v>
+        <v>2.186734676361084</v>
       </c>
       <c r="H35" t="n">
-        <v>2.90904712677002</v>
+        <v>2.418280124664307</v>
       </c>
       <c r="I35" t="n">
-        <v>2.842710256576538</v>
+        <v>2.258721351623535</v>
       </c>
       <c r="J35" t="n">
-        <v>2.657477617263794</v>
+        <v>2.423281908035278</v>
       </c>
       <c r="K35" t="n">
-        <v>2.686375141143799</v>
+        <v>2.242251396179199</v>
       </c>
       <c r="L35" t="n">
-        <v>2.679575967788696</v>
+        <v>2.278143119812012</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>2.092820644378662</v>
+        <v>2.000597953796387</v>
       </c>
       <c r="C36" t="n">
-        <v>2.039473295211792</v>
+        <v>1.830620765686035</v>
       </c>
       <c r="D36" t="n">
-        <v>2.168503761291504</v>
+        <v>1.911251783370972</v>
       </c>
       <c r="E36" t="n">
-        <v>2.164256811141968</v>
+        <v>1.977414846420288</v>
       </c>
       <c r="F36" t="n">
-        <v>2.024552822113037</v>
+        <v>2.10867714881897</v>
       </c>
       <c r="G36" t="n">
-        <v>2.116859912872314</v>
+        <v>2.526513338088989</v>
       </c>
       <c r="H36" t="n">
-        <v>2.128411531448364</v>
+        <v>1.851083993911743</v>
       </c>
       <c r="I36" t="n">
-        <v>2.246585845947266</v>
+        <v>1.973410844802856</v>
       </c>
       <c r="J36" t="n">
-        <v>2.388374805450439</v>
+        <v>1.819531679153442</v>
       </c>
       <c r="K36" t="n">
-        <v>2.082763433456421</v>
+        <v>1.942240715026855</v>
       </c>
       <c r="L36" t="n">
-        <v>2.145260286331177</v>
+        <v>1.994134306907654</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.616621494293213</v>
+        <v>2.113336324691772</v>
       </c>
       <c r="C37" t="n">
-        <v>2.564164400100708</v>
+        <v>2.528157711029053</v>
       </c>
       <c r="D37" t="n">
-        <v>2.324796438217163</v>
+        <v>2.147417068481445</v>
       </c>
       <c r="E37" t="n">
-        <v>2.263003826141357</v>
+        <v>2.066542148590088</v>
       </c>
       <c r="F37" t="n">
-        <v>2.409609794616699</v>
+        <v>2.262886524200439</v>
       </c>
       <c r="G37" t="n">
-        <v>2.405501365661621</v>
+        <v>2.238823890686035</v>
       </c>
       <c r="H37" t="n">
-        <v>2.519311428070068</v>
+        <v>2.093232870101929</v>
       </c>
       <c r="I37" t="n">
-        <v>2.37357759475708</v>
+        <v>2.130485534667969</v>
       </c>
       <c r="J37" t="n">
-        <v>2.453805923461914</v>
+        <v>2.154205083847046</v>
       </c>
       <c r="K37" t="n">
-        <v>2.355450868606567</v>
+        <v>2.272643327713013</v>
       </c>
       <c r="L37" t="n">
-        <v>2.428584313392639</v>
+        <v>2.200773048400879</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.598332405090332</v>
+        <v>2.270186424255371</v>
       </c>
       <c r="C38" t="n">
-        <v>2.651325941085815</v>
+        <v>2.507656097412109</v>
       </c>
       <c r="D38" t="n">
-        <v>2.596323251724243</v>
+        <v>2.467942953109741</v>
       </c>
       <c r="E38" t="n">
-        <v>2.915127515792847</v>
+        <v>2.521564960479736</v>
       </c>
       <c r="F38" t="n">
-        <v>2.631509304046631</v>
+        <v>2.54468846321106</v>
       </c>
       <c r="G38" t="n">
-        <v>2.482146024703979</v>
+        <v>2.557258367538452</v>
       </c>
       <c r="H38" t="n">
-        <v>3.014958381652832</v>
+        <v>2.400281667709351</v>
       </c>
       <c r="I38" t="n">
-        <v>2.741619825363159</v>
+        <v>2.49637246131897</v>
       </c>
       <c r="J38" t="n">
-        <v>2.750949144363403</v>
+        <v>2.411887407302856</v>
       </c>
       <c r="K38" t="n">
-        <v>2.821135282516479</v>
+        <v>2.557740926742554</v>
       </c>
       <c r="L38" t="n">
-        <v>2.720342707633972</v>
+        <v>2.47355797290802</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.079665899276733</v>
+        <v>2.288073778152466</v>
       </c>
       <c r="C39" t="n">
-        <v>2.237176418304443</v>
+        <v>2.345723628997803</v>
       </c>
       <c r="D39" t="n">
-        <v>2.901265144348145</v>
+        <v>2.135868072509766</v>
       </c>
       <c r="E39" t="n">
-        <v>2.651965618133545</v>
+        <v>2.379941463470459</v>
       </c>
       <c r="F39" t="n">
-        <v>2.407963514328003</v>
+        <v>2.289195775985718</v>
       </c>
       <c r="G39" t="n">
-        <v>2.333795547485352</v>
+        <v>2.155557870864868</v>
       </c>
       <c r="H39" t="n">
-        <v>2.102819681167603</v>
+        <v>2.140587091445923</v>
       </c>
       <c r="I39" t="n">
-        <v>2.630972862243652</v>
+        <v>2.47667670249939</v>
       </c>
       <c r="J39" t="n">
-        <v>2.200922250747681</v>
+        <v>2.052599906921387</v>
       </c>
       <c r="K39" t="n">
-        <v>2.371430635452271</v>
+        <v>2.256386995315552</v>
       </c>
       <c r="L39" t="n">
-        <v>2.391797757148743</v>
+        <v>2.252061128616333</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.276982545852661</v>
+        <v>2.055356979370117</v>
       </c>
       <c r="C40" t="n">
-        <v>2.388425588607788</v>
+        <v>2.207189559936523</v>
       </c>
       <c r="D40" t="n">
-        <v>2.346595287322998</v>
+        <v>2.029186010360718</v>
       </c>
       <c r="E40" t="n">
-        <v>2.233975887298584</v>
+        <v>1.99751091003418</v>
       </c>
       <c r="F40" t="n">
-        <v>2.355661392211914</v>
+        <v>2.154486894607544</v>
       </c>
       <c r="G40" t="n">
-        <v>2.227695465087891</v>
+        <v>2.160041332244873</v>
       </c>
       <c r="H40" t="n">
-        <v>2.329181909561157</v>
+        <v>2.191412925720215</v>
       </c>
       <c r="I40" t="n">
-        <v>2.445900917053223</v>
+        <v>2.18270468711853</v>
       </c>
       <c r="J40" t="n">
-        <v>2.361137628555298</v>
+        <v>2.104175329208374</v>
       </c>
       <c r="K40" t="n">
-        <v>2.379456996917725</v>
+        <v>1.943796396255493</v>
       </c>
       <c r="L40" t="n">
-        <v>2.334501361846924</v>
+        <v>2.102586102485657</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.44893217086792</v>
+        <v>2.28577446937561</v>
       </c>
       <c r="C41" t="n">
-        <v>2.597442388534546</v>
+        <v>2.272936820983887</v>
       </c>
       <c r="D41" t="n">
-        <v>2.570986270904541</v>
+        <v>2.192073106765747</v>
       </c>
       <c r="E41" t="n">
-        <v>2.37215256690979</v>
+        <v>2.26198148727417</v>
       </c>
       <c r="F41" t="n">
-        <v>2.4009850025177</v>
+        <v>2.271277189254761</v>
       </c>
       <c r="G41" t="n">
-        <v>2.411688566207886</v>
+        <v>2.303746461868286</v>
       </c>
       <c r="H41" t="n">
-        <v>2.387614488601685</v>
+        <v>2.297738552093506</v>
       </c>
       <c r="I41" t="n">
-        <v>2.514330148696899</v>
+        <v>2.227208614349365</v>
       </c>
       <c r="J41" t="n">
-        <v>2.450814008712769</v>
+        <v>2.194656133651733</v>
       </c>
       <c r="K41" t="n">
-        <v>2.698861360549927</v>
+        <v>2.300171375274658</v>
       </c>
       <c r="L41" t="n">
-        <v>2.485380697250366</v>
+        <v>2.260756421089172</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>2.470679998397827</v>
+        <v>1.916027784347534</v>
       </c>
       <c r="C42" t="n">
-        <v>2.280279874801636</v>
+        <v>2.114816904067993</v>
       </c>
       <c r="D42" t="n">
-        <v>2.203092575073242</v>
+        <v>1.896117687225342</v>
       </c>
       <c r="E42" t="n">
-        <v>2.398419380187988</v>
+        <v>2.088934659957886</v>
       </c>
       <c r="F42" t="n">
-        <v>2.056440114974976</v>
+        <v>1.856478452682495</v>
       </c>
       <c r="G42" t="n">
-        <v>2.212009429931641</v>
+        <v>2.110334396362305</v>
       </c>
       <c r="H42" t="n">
-        <v>2.341898202896118</v>
+        <v>1.999131679534912</v>
       </c>
       <c r="I42" t="n">
-        <v>2.063582181930542</v>
+        <v>1.946107387542725</v>
       </c>
       <c r="J42" t="n">
-        <v>2.387306213378906</v>
+        <v>1.847186326980591</v>
       </c>
       <c r="K42" t="n">
-        <v>2.195292949676514</v>
+        <v>1.973973035812378</v>
       </c>
       <c r="L42" t="n">
-        <v>2.260900092124939</v>
+        <v>1.974910831451416</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.359307765960693</v>
+        <v>2.287108898162842</v>
       </c>
       <c r="C43" t="n">
-        <v>2.506691217422485</v>
+        <v>2.321374416351318</v>
       </c>
       <c r="D43" t="n">
-        <v>2.375750541687012</v>
+        <v>2.221036911010742</v>
       </c>
       <c r="E43" t="n">
-        <v>2.335340261459351</v>
+        <v>2.317594289779663</v>
       </c>
       <c r="F43" t="n">
-        <v>2.537664890289307</v>
+        <v>2.189053773880005</v>
       </c>
       <c r="G43" t="n">
-        <v>2.365501642227173</v>
+        <v>2.270804166793823</v>
       </c>
       <c r="H43" t="n">
-        <v>2.242991924285889</v>
+        <v>2.153456687927246</v>
       </c>
       <c r="I43" t="n">
-        <v>2.455152034759521</v>
+        <v>2.179210901260376</v>
       </c>
       <c r="J43" t="n">
-        <v>2.172462224960327</v>
+        <v>2.131183624267578</v>
       </c>
       <c r="K43" t="n">
-        <v>2.195661544799805</v>
+        <v>2.259229898452759</v>
       </c>
       <c r="L43" t="n">
-        <v>2.354652404785156</v>
+        <v>2.233005356788635</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.282901525497437</v>
+        <v>2.178278207778931</v>
       </c>
       <c r="C44" t="n">
-        <v>2.429849624633789</v>
+        <v>2.020235061645508</v>
       </c>
       <c r="D44" t="n">
-        <v>2.328833341598511</v>
+        <v>2.033018350601196</v>
       </c>
       <c r="E44" t="n">
-        <v>2.287705898284912</v>
+        <v>1.995348215103149</v>
       </c>
       <c r="F44" t="n">
-        <v>2.206934690475464</v>
+        <v>2.028158664703369</v>
       </c>
       <c r="G44" t="n">
-        <v>2.361422538757324</v>
+        <v>1.897882223129272</v>
       </c>
       <c r="H44" t="n">
-        <v>2.577957391738892</v>
+        <v>2.100277423858643</v>
       </c>
       <c r="I44" t="n">
-        <v>2.284263610839844</v>
+        <v>1.943792343139648</v>
       </c>
       <c r="J44" t="n">
-        <v>2.237879753112793</v>
+        <v>2.025267601013184</v>
       </c>
       <c r="K44" t="n">
-        <v>2.239293813705444</v>
+        <v>2.065800666809082</v>
       </c>
       <c r="L44" t="n">
-        <v>2.323704218864441</v>
+        <v>2.028805875778198</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1.93009877204895</v>
+        <v>2.032519340515137</v>
       </c>
       <c r="C45" t="n">
-        <v>2.08637547492981</v>
+        <v>2.004944086074829</v>
       </c>
       <c r="D45" t="n">
-        <v>2.225372076034546</v>
+        <v>2.09844970703125</v>
       </c>
       <c r="E45" t="n">
-        <v>2.08534049987793</v>
+        <v>2.220781087875366</v>
       </c>
       <c r="F45" t="n">
-        <v>2.164950132369995</v>
+        <v>1.959428310394287</v>
       </c>
       <c r="G45" t="n">
-        <v>2.089888572692871</v>
+        <v>2.137149095535278</v>
       </c>
       <c r="H45" t="n">
-        <v>2.04656195640564</v>
+        <v>2.227753877639771</v>
       </c>
       <c r="I45" t="n">
-        <v>2.043928861618042</v>
+        <v>2.097050905227661</v>
       </c>
       <c r="J45" t="n">
-        <v>2.492972135543823</v>
+        <v>1.911927461624146</v>
       </c>
       <c r="K45" t="n">
-        <v>2.117775678634644</v>
+        <v>1.938677072525024</v>
       </c>
       <c r="L45" t="n">
-        <v>2.128326416015625</v>
+        <v>2.062868094444275</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>2.082801342010498</v>
+        <v>1.940594673156738</v>
       </c>
       <c r="C46" t="n">
-        <v>2.16400146484375</v>
+        <v>2.055436372756958</v>
       </c>
       <c r="D46" t="n">
-        <v>1.896103620529175</v>
+        <v>2.21829080581665</v>
       </c>
       <c r="E46" t="n">
-        <v>1.930692434310913</v>
+        <v>2.175163745880127</v>
       </c>
       <c r="F46" t="n">
-        <v>2.257018089294434</v>
+        <v>2.515028715133667</v>
       </c>
       <c r="G46" t="n">
-        <v>2.23393177986145</v>
+        <v>1.996691226959229</v>
       </c>
       <c r="H46" t="n">
-        <v>2.032710313796997</v>
+        <v>2.700776815414429</v>
       </c>
       <c r="I46" t="n">
-        <v>1.876911878585815</v>
+        <v>2.279903888702393</v>
       </c>
       <c r="J46" t="n">
-        <v>2.307997465133667</v>
+        <v>2.900243759155273</v>
       </c>
       <c r="K46" t="n">
-        <v>2.156865835189819</v>
+        <v>2.294863700866699</v>
       </c>
       <c r="L46" t="n">
-        <v>2.093903422355652</v>
+        <v>2.307699370384216</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.99261736869812</v>
+        <v>2.640937805175781</v>
       </c>
       <c r="C47" t="n">
-        <v>3.027151346206665</v>
+        <v>2.773582935333252</v>
       </c>
       <c r="D47" t="n">
-        <v>2.713929891586304</v>
+        <v>2.525246381759644</v>
       </c>
       <c r="E47" t="n">
-        <v>2.945147752761841</v>
+        <v>2.4324951171875</v>
       </c>
       <c r="F47" t="n">
-        <v>2.866852760314941</v>
+        <v>2.774580478668213</v>
       </c>
       <c r="G47" t="n">
-        <v>2.941505670547485</v>
+        <v>2.62896990776062</v>
       </c>
       <c r="H47" t="n">
-        <v>2.875275611877441</v>
+        <v>2.60004711151123</v>
       </c>
       <c r="I47" t="n">
-        <v>2.949041843414307</v>
+        <v>2.579102754592896</v>
       </c>
       <c r="J47" t="n">
-        <v>2.926196336746216</v>
+        <v>2.708755970001221</v>
       </c>
       <c r="K47" t="n">
-        <v>3.053003787994385</v>
+        <v>2.769593477249146</v>
       </c>
       <c r="L47" t="n">
-        <v>2.929072237014771</v>
+        <v>2.64333119392395</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.531127214431763</v>
+        <v>2.236020803451538</v>
       </c>
       <c r="C48" t="n">
-        <v>2.431820392608643</v>
+        <v>2.121326684951782</v>
       </c>
       <c r="D48" t="n">
-        <v>2.492083787918091</v>
+        <v>2.373652219772339</v>
       </c>
       <c r="E48" t="n">
-        <v>2.34490180015564</v>
+        <v>2.053508281707764</v>
       </c>
       <c r="F48" t="n">
-        <v>2.263681411743164</v>
+        <v>2.406564235687256</v>
       </c>
       <c r="G48" t="n">
-        <v>2.651828765869141</v>
+        <v>2.095396280288696</v>
       </c>
       <c r="H48" t="n">
-        <v>2.361851453781128</v>
+        <v>2.257961511611938</v>
       </c>
       <c r="I48" t="n">
-        <v>2.382833480834961</v>
+        <v>2.22504997253418</v>
       </c>
       <c r="J48" t="n">
-        <v>2.783350706100464</v>
+        <v>3.488411903381348</v>
       </c>
       <c r="K48" t="n">
-        <v>2.461332559585571</v>
+        <v>2.202111482620239</v>
       </c>
       <c r="L48" t="n">
-        <v>2.470481157302856</v>
+        <v>2.346000337600708</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.44467568397522</v>
+        <v>2.22405219078064</v>
       </c>
       <c r="C49" t="n">
-        <v>2.650155305862427</v>
+        <v>2.317801237106323</v>
       </c>
       <c r="D49" t="n">
-        <v>2.675441741943359</v>
+        <v>2.204105615615845</v>
       </c>
       <c r="E49" t="n">
-        <v>2.731543302536011</v>
+        <v>2.324783325195312</v>
       </c>
       <c r="F49" t="n">
-        <v>2.561534643173218</v>
+        <v>2.329769611358643</v>
       </c>
       <c r="G49" t="n">
-        <v>2.678391933441162</v>
+        <v>2.439476251602173</v>
       </c>
       <c r="H49" t="n">
-        <v>2.437443494796753</v>
+        <v>2.380633115768433</v>
       </c>
       <c r="I49" t="n">
-        <v>2.491049289703369</v>
+        <v>2.120328903198242</v>
       </c>
       <c r="J49" t="n">
-        <v>2.439999341964722</v>
+        <v>2.305834293365479</v>
       </c>
       <c r="K49" t="n">
-        <v>2.380118608474731</v>
+        <v>2.228041172027588</v>
       </c>
       <c r="L49" t="n">
-        <v>2.549035334587097</v>
+        <v>2.287482571601868</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.221920013427734</v>
+        <v>2.142271041870117</v>
       </c>
       <c r="C50" t="n">
-        <v>2.276213407516479</v>
+        <v>2.122324466705322</v>
       </c>
       <c r="D50" t="n">
-        <v>2.27591609954834</v>
+        <v>2.177177667617798</v>
       </c>
       <c r="E50" t="n">
-        <v>2.282118082046509</v>
+        <v>2.064479827880859</v>
       </c>
       <c r="F50" t="n">
-        <v>2.3565993309021</v>
+        <v>2.201114177703857</v>
       </c>
       <c r="G50" t="n">
-        <v>2.358595371246338</v>
+        <v>2.203108549118042</v>
       </c>
       <c r="H50" t="n">
-        <v>2.597648143768311</v>
+        <v>1.978708744049072</v>
       </c>
       <c r="I50" t="n">
-        <v>2.12887978553772</v>
+        <v>1.948788642883301</v>
       </c>
       <c r="J50" t="n">
-        <v>2.27945876121521</v>
+        <v>2.311817646026611</v>
       </c>
       <c r="K50" t="n">
-        <v>2.347024202346802</v>
+        <v>1.955769777297974</v>
       </c>
       <c r="L50" t="n">
-        <v>2.312437319755554</v>
+        <v>2.110556054115295</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>2.372310876846313</v>
+        <v>1.965743541717529</v>
       </c>
       <c r="C51" t="n">
-        <v>2.218500375747681</v>
+        <v>1.85603666305542</v>
       </c>
       <c r="D51" t="n">
-        <v>2.295588254928589</v>
+        <v>1.90789794921875</v>
       </c>
       <c r="E51" t="n">
-        <v>2.082718849182129</v>
+        <v>1.907898426055908</v>
       </c>
       <c r="F51" t="n">
-        <v>2.031842708587646</v>
+        <v>1.960756540298462</v>
       </c>
       <c r="G51" t="n">
-        <v>2.310814619064331</v>
+        <v>1.91986608505249</v>
       </c>
       <c r="H51" t="n">
-        <v>2.274202346801758</v>
+        <v>2.021594047546387</v>
       </c>
       <c r="I51" t="n">
-        <v>2.317240715026855</v>
+        <v>1.80417537689209</v>
       </c>
       <c r="J51" t="n">
-        <v>2.115476369857788</v>
+        <v>2.26494288444519</v>
       </c>
       <c r="K51" t="n">
-        <v>2.263557434082031</v>
+        <v>1.846063613891602</v>
       </c>
       <c r="L51" t="n">
-        <v>2.228225255012512</v>
+        <v>1.945497512817383</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.367489137649536</v>
+        <v>2.223679542541504</v>
       </c>
       <c r="C52" t="n">
-        <v>2.413922004699707</v>
+        <v>2.278164319992066</v>
       </c>
       <c r="D52" t="n">
-        <v>2.408528099060058</v>
+        <v>2.271958518028259</v>
       </c>
       <c r="E52" t="n">
-        <v>2.404668736457825</v>
+        <v>2.294777965545654</v>
       </c>
       <c r="F52" t="n">
-        <v>2.33726610660553</v>
+        <v>2.329833059310913</v>
       </c>
       <c r="G52" t="n">
-        <v>2.37438051700592</v>
+        <v>2.274533815383911</v>
       </c>
       <c r="H52" t="n">
-        <v>2.3722775888443</v>
+        <v>2.280410838127136</v>
       </c>
       <c r="I52" t="n">
-        <v>2.408034896850586</v>
+        <v>2.249903416633606</v>
       </c>
       <c r="J52" t="n">
-        <v>2.400135903358459</v>
+        <v>2.294237451553345</v>
       </c>
       <c r="K52" t="n">
-        <v>2.716965956687927</v>
+        <v>2.276575837135315</v>
       </c>
       <c r="L52" t="n">
-        <v>2.420366894721985</v>
+        <v>2.277407476425171</v>
       </c>
     </row>
   </sheetData>
